--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -23,8 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,12 +42,23 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -68,7 +81,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +92,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,27 +133,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -616,242 +644,458 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="11" t="n"/>
-      <c r="R2" s="11" t="n"/>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>龙溪股份</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>600592</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600592.html</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>共筛选出 0 只标的（A:0 B:0 C:0 D:0 E:0）</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="11" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="11" t="n"/>
-      <c r="R3" s="11" t="n"/>
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>600487</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>105.08</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600487.html</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="11" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="11" t="n"/>
-      <c r="M4" s="11" t="n"/>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="11" t="n"/>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="11" t="n"/>
-      <c r="R4" s="11" t="n"/>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>科新发展</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>600234</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600234.html</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="14" t="n"/>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>共筛选出 3 只标的（A:0 B:3 C:0 D:0 E:0）</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
+      <c r="N7" s="14" t="n"/>
+      <c r="O7" s="14" t="n"/>
+      <c r="P7" s="14" t="n"/>
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，MA5&gt;MA10&gt;MA20 -- 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
-      <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="11" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
+      <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌&gt;=3日，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认 -- 仓位10-15%</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="11" t="n"/>
-      <c r="Q6" s="11" t="n"/>
-      <c r="R6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
+      <c r="P9" s="14" t="n"/>
+      <c r="Q9" s="14" t="n"/>
+      <c r="R9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策 -- 仓位5-12%</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="11" t="n"/>
-      <c r="Q7" s="11" t="n"/>
-      <c r="R7" s="11" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
+      <c r="O10" s="14" t="n"/>
+      <c r="P10" s="14" t="n"/>
+      <c r="Q10" s="14" t="n"/>
+      <c r="R10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% -- 仓位3-8%</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="n"/>
-      <c r="Q8" s="11" t="n"/>
-      <c r="R8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
+      <c r="P11" s="14" t="n"/>
+      <c r="Q11" s="14" t="n"/>
+      <c r="R11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20+/-3%+连3日缩量+站回MA5放量 -- 仓位8-15%</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="11" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="n"/>
-      <c r="Q10" s="11" t="n"/>
-      <c r="R10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="14" t="n"/>
+      <c r="P12" s="14" t="n"/>
+      <c r="Q12" s="14" t="n"/>
+      <c r="R12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="14" t="n"/>
+      <c r="P13" s="14" t="n"/>
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>仅供参考，不构成投资建议</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
-      <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="11" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="14" t="n"/>
+      <c r="P14" s="14" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A7:R7"/>
     <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A14:R14"/>
     <mergeCell ref="A9:R9"/>
     <mergeCell ref="A8:R8"/>
     <mergeCell ref="A6:R6"/>
+    <mergeCell ref="A12:R12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -871,288 +1115,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>A股短线选股筛选条件 -- v6.5.1</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
-      <c r="C1" s="11" t="n"/>
-      <c r="D1" s="11" t="n"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>v6.5.1</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>更新日期</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>预测日期</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>数据日期</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>市场环境</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>总仓位上限</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>搜索预算</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>北向阈值</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>3000万</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>策略集中度上限</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>置信度仓位联动</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>启用</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>熔断阈值</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
+      <c r="A14" s="9" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>筛选管道</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>原始标的池</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>500只</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>硬排除后</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>201只</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>信号过滤后</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>35只</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>策略匹配后</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>0只</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>14只</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>行业限制后</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>0只</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>3只</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>新闻筛查后</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>0只</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>3只</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>最终推荐</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>0只</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>3只</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1178,4042 +1422,4042 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>排除规则</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>600005</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>武钢股份</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.71&lt;5</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>600008</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>首创环保</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.16&lt;5</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>600010</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>包钢股份</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.39&lt;5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>600016</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>民生银行</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.63&lt;5</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>600017</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>XD日照港</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.69&lt;5</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>600020</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>中原高速</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.96&lt;5</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>600022</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>山东钢铁</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.33&lt;5</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>600028</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>中国石化</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.94&lt;5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>600033</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>福建高速</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.56&lt;5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>600035</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>楚天高速</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.79&lt;5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>600050</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>中国联通</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.37&lt;5</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>600052</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>东望时代</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.65&lt;5</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>600053</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>*ST九鼎</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>600063</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>皖维高新</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>600067</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>冠城新材</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.48&lt;5</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>600069</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>退市银鸽</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.28&lt;5</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>600070</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>*ST富润</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.42&lt;5</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>600074</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>退市保千</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.17&lt;5</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>600075</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>新疆天业</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.75&lt;5</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>600076</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>康欣新材</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.47&lt;5</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>600077</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>*ST宋都</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>600079</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>ST人福</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>600080</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>ST金花</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.78&lt;5</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>600082</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>ST海泰</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.05&lt;5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>600083</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>*ST博信</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.92&lt;5</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>600084</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>*ST尼雅</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.27&lt;5</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>600086</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>退市金钰</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.16&lt;5</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>600090</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>退市济堂</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.27&lt;5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>600091</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>退市明科</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.76&lt;5</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>600093</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>退市易见</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.50&lt;5</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>600094</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>大名城</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.90&lt;5</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>600103</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>青山纸业</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>600107</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>*ST尔雅</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>600108</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>亚盛集团</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.59&lt;5</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>600112</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>*ST天成</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.73&lt;5</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>600115</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>中国东航</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.90&lt;5</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>600117</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>西宁特钢</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.27&lt;5</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>600119</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>*ST长投</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.84&lt;5</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>600120</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>浙江东方</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.47&lt;5</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>600121</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>郑州煤电</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.51&lt;5</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>600122</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>*ST宏图</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.38&lt;5</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>600130</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>波导股份</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.53&lt;5</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>600136</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>ST明诚</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.47&lt;5</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>600139</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>*ST西源</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.74&lt;5</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>600145</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>退市新亿</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.34&lt;5</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>600146</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>退市环球</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.22&lt;5</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>600157</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>永泰能源</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.70&lt;5</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>600159</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>大龙地产</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.63&lt;5</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>600162</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>香江控股</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.47&lt;5</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>600163</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>中闽能源</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>L1-规则12:涨幅9.7%&gt;7%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>600165</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>ST宁科</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.83&lt;5</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>600166</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>福田汽车</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.10&lt;5</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>600168</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>武汉控股</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.46&lt;5</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>600169</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>ST太重</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.24&lt;5</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>600170</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>上海建工</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.42&lt;5</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>600175</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>退市美都</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.21&lt;5</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>600179</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>安通控股</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.56&lt;5</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>600180</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>*ST瑞茂</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.32&lt;5</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>600183</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>生益科技</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>L1-规则4:股价151.28&gt;100</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>600187</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>*ST国中</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.52&lt;5</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>600190</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>退市锦港</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.63&lt;5</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>600193</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>退市创兴</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.16&lt;5</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n">
+      <c r="A64" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>600200</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>退市苏吴</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>600208</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>衢州发展</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.97&lt;5</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="n">
+      <c r="A66" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>600209</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>退市罗顿</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.18&lt;5</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>600213</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>*ST亚星</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>600217</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>中再资环</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.15&lt;5</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>600219</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>南山铝业</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.73&lt;5</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>600220</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>ST阳光</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>600221</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>海航控股</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D71" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.53&lt;5</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="n">
+      <c r="A72" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>600225</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>退市卓朗</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="n">
+      <c r="A73" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>600227</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>赤天化</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D73" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.87&lt;5</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="n">
+      <c r="A74" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>600229</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>城市传媒</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="n">
+      <c r="A75" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>600231</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>凌钢股份</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.89&lt;5</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="n">
+      <c r="A76" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>600238</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>*ST椰岛</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.91&lt;5</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>600239</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>ST云城</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.42&lt;5</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="n">
+      <c r="A78" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>600240</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>退市华业</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="n">
+      <c r="A79" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>600242</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>退市中昌</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.25&lt;5</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="n">
+      <c r="A80" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>600243</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>*ST海华</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.02&lt;5</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="n">
+      <c r="A81" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>600247</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>*ST成城</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.65&lt;5</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="n">
+      <c r="A82" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>600248</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>陕建股份</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.02&lt;5</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="n">
+      <c r="A83" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>600252</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>中恒集团</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.16&lt;5</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="n">
+      <c r="A84" s="10" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>600255</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>鑫科材料</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.15&lt;5</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="n">
+      <c r="A85" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>600260</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>*ST凯乐</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D85" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.47&lt;5</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="n">
+      <c r="A86" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>600261</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>阳光照明</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.19&lt;5</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="n">
+      <c r="A87" s="10" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>600265</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>*ST景谷</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="n">
+      <c r="A88" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>600266</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>城建发展</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.43&lt;5</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="n">
+      <c r="A89" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>600269</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>赣粤高速</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.20&lt;5</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="n">
+      <c r="A90" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>600275</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>退市昌鱼</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="n">
+      <c r="A91" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>600277</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>ST亿利</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D91" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.38&lt;5</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="n">
+      <c r="A92" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>600279</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>重庆港</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.44&lt;5</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="n">
+      <c r="A93" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>600280</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>中央商场</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.93&lt;5</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="n">
+      <c r="A94" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>600281</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>华阳新材</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>600282</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="10" t="inlineStr">
         <is>
           <t>南钢股份</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.84&lt;5</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="n">
+      <c r="A96" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>600287</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>苏豪时尚</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="n">
+      <c r="A97" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>600289</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>ST信通</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D97" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="n">
+      <c r="A98" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>600290</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>*ST华仪</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="n">
+      <c r="A99" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>600291</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>退市西水</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.89&lt;5</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="n">
+      <c r="A100" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>600292</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>电投水电</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D100" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="n">
+      <c r="A101" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>600293</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>三峡新材</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.41&lt;5</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="n">
+      <c r="A102" s="10" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>600297</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>广汇汽车</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.78&lt;5</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="7" t="n">
+      <c r="A103" s="10" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>600300</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>维维股份</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.07&lt;5</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="n">
+      <c r="A104" s="10" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>600301</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>华锡有色</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
         <is>
           <t>L1-规则12:涨幅7.6%&gt;7%</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="n">
+      <c r="A105" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>600302</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>ST标准</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="n">
+      <c r="A106" s="10" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>600303</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>曙光股份</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.04&lt;5</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="10" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>600306</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>退市商城</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="D107" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="n">
+      <c r="A108" s="10" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>600307</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>酒钢宏兴</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.57&lt;5</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="n">
+      <c r="A109" s="10" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>600308</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>华泰股份</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.36&lt;5</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="7" t="n">
+      <c r="A110" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>600310</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>广西能源</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.63&lt;5</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="n">
+      <c r="A111" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>600311</t>
         </is>
       </c>
-      <c r="C111" s="7" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>*ST荣华</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr">
+      <c r="D111" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.61&lt;5</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="n">
+      <c r="A112" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>600317</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>营口港</t>
         </is>
       </c>
-      <c r="D112" s="7" t="inlineStr">
+      <c r="D112" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.60&lt;5</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="n">
+      <c r="A113" s="10" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>600320</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>振华重工</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr">
+      <c r="D113" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="7" t="n">
+      <c r="A114" s="10" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>600321</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>正源股份</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D114" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.50&lt;5</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="n">
+      <c r="A115" s="10" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B115" s="10" t="inlineStr">
         <is>
           <t>600322</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>津投城开</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D115" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.68&lt;5</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="7" t="n">
+      <c r="A116" s="10" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B116" s="10" t="inlineStr">
         <is>
           <t>600325</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>华发股份</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D116" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.63&lt;5</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="10" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>600327</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>大东方</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D117" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="7" t="n">
+      <c r="A118" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>600337</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>ST美克</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D118" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="7" t="n">
+      <c r="A119" s="10" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B119" s="10" t="inlineStr">
         <is>
           <t>600339</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>中油工程</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="D119" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.31&lt;5</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="7" t="n">
+      <c r="A120" s="10" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>600340</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>*ST华幸</t>
         </is>
       </c>
-      <c r="D120" s="7" t="inlineStr">
+      <c r="D120" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.33&lt;5</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="7" t="n">
+      <c r="A121" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>600346</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>恒力石化</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr">
+      <c r="D121" s="10" t="inlineStr">
         <is>
           <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="n">
+      <c r="A122" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>600355</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>*ST精伦</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.58&lt;5</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="7" t="n">
+      <c r="A123" s="10" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B123" s="10" t="inlineStr">
         <is>
           <t>600361</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>创新新材</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
+      <c r="D123" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="7" t="n">
+      <c r="A124" s="10" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>600362</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>江西铜业</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D124" s="10" t="inlineStr">
         <is>
           <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="7" t="n">
+      <c r="A125" s="10" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>600365</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>ST通葡</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="D125" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.55&lt;5</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="7" t="n">
+      <c r="A126" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>600368</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>五洲交通</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.78&lt;5</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="n">
+      <c r="A127" s="10" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>600369</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>西南证券</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D127" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="7" t="n">
+      <c r="A128" s="10" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>600370</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>*ST三房</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.46&lt;5</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="n">
+      <c r="A129" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>600375</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>汉马科技</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D129" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.94&lt;5</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="7" t="n">
+      <c r="A130" s="10" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>600376</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>首开股份</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr">
+      <c r="D130" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.40&lt;5</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="7" t="n">
+      <c r="A131" s="10" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B131" s="10" t="inlineStr">
         <is>
           <t>600378</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>XD昊华科</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
+      <c r="D131" s="10" t="inlineStr">
         <is>
           <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="n">
+      <c r="A132" s="10" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>600381</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>*ST春天</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="7" t="n">
+      <c r="A133" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B133" s="10" t="inlineStr">
         <is>
           <t>600383</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>金地集团</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="D133" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.51&lt;5</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="7" t="n">
+      <c r="A134" s="10" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>600385</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>退市金泰</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
+      <c r="D134" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.20&lt;5</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="7" t="n">
+      <c r="A135" s="10" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="7" t="inlineStr">
+      <c r="B135" s="10" t="inlineStr">
         <is>
           <t>600386</t>
         </is>
       </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="C135" s="10" t="inlineStr">
         <is>
           <t>北巴传媒</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
+      <c r="D135" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="7" t="n">
+      <c r="A136" s="10" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>600387</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C136" s="10" t="inlineStr">
         <is>
           <t>退市海越</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
+      <c r="D136" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.94&lt;5</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="7" t="n">
+      <c r="A137" s="10" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="7" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>600390</t>
         </is>
       </c>
-      <c r="C137" s="7" t="inlineStr">
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>五矿资本</t>
         </is>
       </c>
-      <c r="D137" s="7" t="inlineStr">
+      <c r="D137" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.65&lt;5</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="7" t="n">
+      <c r="A138" s="10" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>600391</t>
         </is>
       </c>
-      <c r="C138" s="7" t="inlineStr">
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>航发科技</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="7" t="n">
+      <c r="A139" s="10" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="7" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>600393</t>
         </is>
       </c>
-      <c r="C139" s="7" t="inlineStr">
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>ST粤泰</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
+      <c r="D139" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="7" t="n">
+      <c r="A140" s="10" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>600399</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>抚顺特钢</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.32&lt;5</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="7" t="n">
+      <c r="A141" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>600400</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>红豆股份</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.61&lt;5</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="7" t="n">
+      <c r="A142" s="10" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>600401</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>退市海润</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.15&lt;5</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="7" t="n">
+      <c r="A143" s="10" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="B143" s="10" t="inlineStr">
         <is>
           <t>600403</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C143" s="10" t="inlineStr">
         <is>
           <t>大有能源</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
+      <c r="D143" s="10" t="inlineStr">
         <is>
           <t>L1-规则22:跌停-9.9%</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="7" t="n">
+      <c r="A144" s="10" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>600405</t>
         </is>
       </c>
-      <c r="C144" s="7" t="inlineStr">
+      <c r="C144" s="10" t="inlineStr">
         <is>
           <t>动力源</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr">
+      <c r="D144" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.26&lt;5</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="7" t="n">
+      <c r="A145" s="10" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>600408</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C145" s="10" t="inlineStr">
         <is>
           <t>安泰集团</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="D145" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.88&lt;5</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="7" t="n">
+      <c r="A146" s="10" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>600421</t>
         </is>
       </c>
-      <c r="C146" s="7" t="inlineStr">
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>退市华嵘</t>
         </is>
       </c>
-      <c r="D146" s="7" t="inlineStr">
+      <c r="D146" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="n">
+      <c r="A147" s="10" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>600423</t>
         </is>
       </c>
-      <c r="C147" s="7" t="inlineStr">
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>*ST柳化</t>
         </is>
       </c>
-      <c r="D147" s="7" t="inlineStr">
+      <c r="D147" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.48&lt;5</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="7" t="n">
+      <c r="A148" s="10" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>600425</t>
         </is>
       </c>
-      <c r="C148" s="7" t="inlineStr">
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>XD青松建</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr">
+      <c r="D148" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.54&lt;5</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="7" t="n">
+      <c r="A149" s="10" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="7" t="inlineStr">
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>600429</t>
         </is>
       </c>
-      <c r="C149" s="7" t="inlineStr">
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>三元股份</t>
         </is>
       </c>
-      <c r="D149" s="7" t="inlineStr">
+      <c r="D149" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="7" t="n">
+      <c r="A150" s="10" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>600432</t>
         </is>
       </c>
-      <c r="C150" s="7" t="inlineStr">
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>退市吉恩</t>
         </is>
       </c>
-      <c r="D150" s="7" t="inlineStr">
+      <c r="D150" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.38&lt;5</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="7" t="n">
+      <c r="A151" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="7" t="inlineStr">
+      <c r="B151" s="10" t="inlineStr">
         <is>
           <t>600433</t>
         </is>
       </c>
-      <c r="C151" s="7" t="inlineStr">
+      <c r="C151" s="10" t="inlineStr">
         <is>
           <t>冠豪高新</t>
         </is>
       </c>
-      <c r="D151" s="7" t="inlineStr">
+      <c r="D151" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.53&lt;5</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="7" t="n">
+      <c r="A152" s="10" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="7" t="inlineStr">
+      <c r="B152" s="10" t="inlineStr">
         <is>
           <t>600436</t>
         </is>
       </c>
-      <c r="C152" s="7" t="inlineStr">
+      <c r="C152" s="10" t="inlineStr">
         <is>
           <t>片仔癀</t>
         </is>
       </c>
-      <c r="D152" s="7" t="inlineStr">
+      <c r="D152" s="10" t="inlineStr">
         <is>
           <t>L1-规则4:股价119.56&gt;100</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="7" t="n">
+      <c r="A153" s="10" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="B153" s="10" t="inlineStr">
         <is>
           <t>600439</t>
         </is>
       </c>
-      <c r="C153" s="7" t="inlineStr">
+      <c r="C153" s="10" t="inlineStr">
         <is>
           <t>瑞贝卡</t>
         </is>
       </c>
-      <c r="D153" s="7" t="inlineStr">
+      <c r="D153" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.27&lt;5</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="n">
+      <c r="A154" s="10" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B154" s="10" t="inlineStr">
         <is>
           <t>600448</t>
         </is>
       </c>
-      <c r="C154" s="7" t="inlineStr">
+      <c r="C154" s="10" t="inlineStr">
         <is>
           <t>华纺股份</t>
         </is>
       </c>
-      <c r="D154" s="7" t="inlineStr">
+      <c r="D154" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="7" t="n">
+      <c r="A155" s="10" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="7" t="inlineStr">
+      <c r="B155" s="10" t="inlineStr">
         <is>
           <t>600462</t>
         </is>
       </c>
-      <c r="C155" s="7" t="inlineStr">
+      <c r="C155" s="10" t="inlineStr">
         <is>
           <t>退市九有</t>
         </is>
       </c>
-      <c r="D155" s="7" t="inlineStr">
+      <c r="D155" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.21&lt;5</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="7" t="n">
+      <c r="A156" s="10" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="7" t="inlineStr">
+      <c r="B156" s="10" t="inlineStr">
         <is>
           <t>600466</t>
         </is>
       </c>
-      <c r="C156" s="7" t="inlineStr">
+      <c r="C156" s="10" t="inlineStr">
         <is>
           <t>*ST蓝光</t>
         </is>
       </c>
-      <c r="D156" s="7" t="inlineStr">
+      <c r="D156" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.40&lt;5</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="7" t="n">
+      <c r="A157" s="10" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="7" t="inlineStr">
+      <c r="B157" s="10" t="inlineStr">
         <is>
           <t>600467</t>
         </is>
       </c>
-      <c r="C157" s="7" t="inlineStr">
+      <c r="C157" s="10" t="inlineStr">
         <is>
           <t>好当家</t>
         </is>
       </c>
-      <c r="D157" s="7" t="inlineStr">
+      <c r="D157" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="7" t="n">
+      <c r="A158" s="10" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="7" t="inlineStr">
+      <c r="B158" s="10" t="inlineStr">
         <is>
           <t>600476</t>
         </is>
       </c>
-      <c r="C158" s="7" t="inlineStr">
+      <c r="C158" s="10" t="inlineStr">
         <is>
           <t>*ST湘邮</t>
         </is>
       </c>
-      <c r="D158" s="7" t="inlineStr">
+      <c r="D158" s="10" t="inlineStr">
         <is>
           <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="7" t="n">
+      <c r="A159" s="10" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="7" t="inlineStr">
+      <c r="B159" s="10" t="inlineStr">
         <is>
           <t>600477</t>
         </is>
       </c>
-      <c r="C159" s="7" t="inlineStr">
+      <c r="C159" s="10" t="inlineStr">
         <is>
           <t>杭萧钢构</t>
         </is>
       </c>
-      <c r="D159" s="7" t="inlineStr">
+      <c r="D159" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.59&lt;5</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="7" t="n">
+      <c r="A160" s="10" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="B160" s="10" t="inlineStr">
         <is>
           <t>600485</t>
         </is>
       </c>
-      <c r="C160" s="7" t="inlineStr">
+      <c r="C160" s="10" t="inlineStr">
         <is>
           <t>*ST信威</t>
         </is>
       </c>
-      <c r="D160" s="7" t="inlineStr">
+      <c r="D160" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.39&lt;5</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="7" t="n">
+      <c r="A161" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="7" t="inlineStr">
+      <c r="B161" s="10" t="inlineStr">
         <is>
           <t>600488</t>
         </is>
       </c>
-      <c r="C161" s="7" t="inlineStr">
+      <c r="C161" s="10" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="D161" s="7" t="inlineStr">
+      <c r="D161" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.76&lt;5</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="7" t="n">
+      <c r="A162" s="10" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="7" t="inlineStr">
+      <c r="B162" s="10" t="inlineStr">
         <is>
           <t>600491</t>
         </is>
       </c>
-      <c r="C162" s="7" t="inlineStr">
+      <c r="C162" s="10" t="inlineStr">
         <is>
           <t>ST龙元</t>
         </is>
       </c>
-      <c r="D162" s="7" t="inlineStr">
+      <c r="D162" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.31&lt;5</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="7" t="n">
+      <c r="A163" s="10" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="7" t="inlineStr">
+      <c r="B163" s="10" t="inlineStr">
         <is>
           <t>600495</t>
         </is>
       </c>
-      <c r="C163" s="7" t="inlineStr">
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>晋西车轴</t>
         </is>
       </c>
-      <c r="D163" s="7" t="inlineStr">
+      <c r="D163" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.80&lt;5</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="7" t="n">
+      <c r="A164" s="10" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="7" t="inlineStr">
+      <c r="B164" s="10" t="inlineStr">
         <is>
           <t>600496</t>
         </is>
       </c>
-      <c r="C164" s="7" t="inlineStr">
+      <c r="C164" s="10" t="inlineStr">
         <is>
           <t>精工钢构</t>
         </is>
       </c>
-      <c r="D164" s="7" t="inlineStr">
+      <c r="D164" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.84&lt;5</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="7" t="n">
+      <c r="A165" s="10" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="7" t="inlineStr">
+      <c r="B165" s="10" t="inlineStr">
         <is>
           <t>600497</t>
         </is>
       </c>
-      <c r="C165" s="7" t="inlineStr">
+      <c r="C165" s="10" t="inlineStr">
         <is>
           <t>驰宏锌锗</t>
         </is>
       </c>
-      <c r="D165" s="7" t="inlineStr">
+      <c r="D165" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="7" t="n">
+      <c r="A166" s="10" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="7" t="inlineStr">
+      <c r="B166" s="10" t="inlineStr">
         <is>
           <t>600500</t>
         </is>
       </c>
-      <c r="C166" s="7" t="inlineStr">
+      <c r="C166" s="10" t="inlineStr">
         <is>
           <t>中化国际</t>
         </is>
       </c>
-      <c r="D166" s="7" t="inlineStr">
+      <c r="D166" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="7" t="n">
+      <c r="A167" s="10" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="7" t="inlineStr">
+      <c r="B167" s="10" t="inlineStr">
         <is>
           <t>600502</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
+      <c r="C167" s="10" t="inlineStr">
         <is>
           <t>安徽建工</t>
         </is>
       </c>
-      <c r="D167" s="7" t="inlineStr">
+      <c r="D167" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.68&lt;5</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="7" t="n">
+      <c r="A168" s="10" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="7" t="inlineStr">
+      <c r="B168" s="10" t="inlineStr">
         <is>
           <t>600503</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr">
+      <c r="C168" s="10" t="inlineStr">
         <is>
           <t>华丽家族</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr">
+      <c r="D168" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.46&lt;5</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="n">
+      <c r="A169" s="10" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="7" t="inlineStr">
+      <c r="B169" s="10" t="inlineStr">
         <is>
           <t>600507</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr">
+      <c r="C169" s="10" t="inlineStr">
         <is>
           <t>方大特钢</t>
         </is>
       </c>
-      <c r="D169" s="7" t="inlineStr">
+      <c r="D169" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.29&lt;5</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="7" t="n">
+      <c r="A170" s="10" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="7" t="inlineStr">
+      <c r="B170" s="10" t="inlineStr">
         <is>
           <t>600512</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr">
+      <c r="C170" s="10" t="inlineStr">
         <is>
           <t>腾达建设</t>
         </is>
       </c>
-      <c r="D170" s="7" t="inlineStr">
+      <c r="D170" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.08&lt;5</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="7" t="n">
+      <c r="A171" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="7" t="inlineStr">
+      <c r="B171" s="10" t="inlineStr">
         <is>
           <t>600515</t>
         </is>
       </c>
-      <c r="C171" s="7" t="inlineStr">
+      <c r="C171" s="10" t="inlineStr">
         <is>
           <t>海南机场</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
+      <c r="D171" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.98&lt;5</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="7" t="n">
+      <c r="A172" s="10" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="7" t="inlineStr">
+      <c r="B172" s="10" t="inlineStr">
         <is>
           <t>600517</t>
         </is>
       </c>
-      <c r="C172" s="7" t="inlineStr">
+      <c r="C172" s="10" t="inlineStr">
         <is>
           <t>国网英大</t>
         </is>
       </c>
-      <c r="D172" s="7" t="inlineStr">
+      <c r="D172" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="7" t="n">
+      <c r="A173" s="10" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B173" s="10" t="inlineStr">
         <is>
           <t>600518</t>
         </is>
       </c>
-      <c r="C173" s="7" t="inlineStr">
+      <c r="C173" s="10" t="inlineStr">
         <is>
           <t>康美药业</t>
         </is>
       </c>
-      <c r="D173" s="7" t="inlineStr">
+      <c r="D173" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.40&lt;5</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="7" t="n">
+      <c r="A174" s="10" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="7" t="inlineStr">
+      <c r="B174" s="10" t="inlineStr">
         <is>
           <t>600519</t>
         </is>
       </c>
-      <c r="C174" s="7" t="inlineStr">
+      <c r="C174" s="10" t="inlineStr">
         <is>
           <t>贵州茅台</t>
         </is>
       </c>
-      <c r="D174" s="7" t="inlineStr">
+      <c r="D174" s="10" t="inlineStr">
         <is>
           <t>L1-规则4:股价1291.91&gt;100</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="7" t="n">
+      <c r="A175" s="10" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="B175" s="10" t="inlineStr">
         <is>
           <t>600525</t>
         </is>
       </c>
-      <c r="C175" s="7" t="inlineStr">
+      <c r="C175" s="10" t="inlineStr">
         <is>
           <t>ST长园</t>
         </is>
       </c>
-      <c r="D175" s="7" t="inlineStr">
+      <c r="D175" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.99&lt;5</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="7" t="n">
+      <c r="A176" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="7" t="inlineStr">
+      <c r="B176" s="10" t="inlineStr">
         <is>
           <t>600526</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr">
+      <c r="C176" s="10" t="inlineStr">
         <is>
           <t>菲达环保</t>
         </is>
       </c>
-      <c r="D176" s="7" t="inlineStr">
+      <c r="D176" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.49&lt;5</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="7" t="n">
+      <c r="A177" s="10" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="7" t="inlineStr">
+      <c r="B177" s="10" t="inlineStr">
         <is>
           <t>600527</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr">
+      <c r="C177" s="10" t="inlineStr">
         <is>
           <t>江南高纤</t>
         </is>
       </c>
-      <c r="D177" s="7" t="inlineStr">
+      <c r="D177" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.32&lt;5</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="7" t="n">
+      <c r="A178" s="10" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="7" t="inlineStr">
+      <c r="B178" s="10" t="inlineStr">
         <is>
           <t>600531</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr">
+      <c r="C178" s="10" t="inlineStr">
         <is>
           <t>豫光金铅</t>
         </is>
       </c>
-      <c r="D178" s="7" t="inlineStr">
+      <c r="D178" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="7" t="n">
+      <c r="A179" s="10" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="B179" s="10" t="inlineStr">
         <is>
           <t>600532</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr">
+      <c r="C179" s="10" t="inlineStr">
         <is>
           <t>退市未来</t>
         </is>
       </c>
-      <c r="D179" s="7" t="inlineStr">
+      <c r="D179" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.72&lt;5</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="7" t="n">
+      <c r="A180" s="10" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B180" s="10" t="inlineStr">
         <is>
           <t>600533</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
+      <c r="C180" s="10" t="inlineStr">
         <is>
           <t>栖霞建设</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr">
+      <c r="D180" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="7" t="n">
+      <c r="A181" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="7" t="inlineStr">
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>600536</t>
         </is>
       </c>
-      <c r="C181" s="7" t="inlineStr">
+      <c r="C181" s="10" t="inlineStr">
         <is>
           <t>中国软件</t>
         </is>
       </c>
-      <c r="D181" s="7" t="inlineStr">
+      <c r="D181" s="10" t="inlineStr">
         <is>
           <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="7" t="n">
+      <c r="A182" s="10" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="7" t="inlineStr">
+      <c r="B182" s="10" t="inlineStr">
         <is>
           <t>600537</t>
         </is>
       </c>
-      <c r="C182" s="7" t="inlineStr">
+      <c r="C182" s="10" t="inlineStr">
         <is>
           <t>*ST亿晶</t>
         </is>
       </c>
-      <c r="D182" s="7" t="inlineStr">
+      <c r="D182" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.58&lt;5</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="7" t="n">
+      <c r="A183" s="10" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="7" t="inlineStr">
+      <c r="B183" s="10" t="inlineStr">
         <is>
           <t>600539</t>
         </is>
       </c>
-      <c r="C183" s="7" t="inlineStr">
+      <c r="C183" s="10" t="inlineStr">
         <is>
           <t>狮头股份</t>
         </is>
       </c>
-      <c r="D183" s="7" t="inlineStr">
+      <c r="D183" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="7" t="n">
+      <c r="A184" s="10" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="7" t="inlineStr">
+      <c r="B184" s="10" t="inlineStr">
         <is>
           <t>600540</t>
         </is>
       </c>
-      <c r="C184" s="7" t="inlineStr">
+      <c r="C184" s="10" t="inlineStr">
         <is>
           <t>新赛股份</t>
         </is>
       </c>
-      <c r="D184" s="7" t="inlineStr">
+      <c r="D184" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.46&lt;5</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="7" t="n">
+      <c r="A185" s="10" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B185" s="10" t="inlineStr">
         <is>
           <t>600543</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
+      <c r="C185" s="10" t="inlineStr">
         <is>
           <t>*ST莫高</t>
         </is>
       </c>
-      <c r="D185" s="7" t="inlineStr">
+      <c r="D185" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.22&lt;5</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="7" t="n">
+      <c r="A186" s="10" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="B186" s="10" t="inlineStr">
         <is>
           <t>600555</t>
         </is>
       </c>
-      <c r="C186" s="7" t="inlineStr">
+      <c r="C186" s="10" t="inlineStr">
         <is>
           <t>退市海创</t>
         </is>
       </c>
-      <c r="D186" s="7" t="inlineStr">
+      <c r="D186" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="7" t="n">
+      <c r="A187" s="10" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="B187" s="10" t="inlineStr">
         <is>
           <t>600556</t>
         </is>
       </c>
-      <c r="C187" s="7" t="inlineStr">
+      <c r="C187" s="10" t="inlineStr">
         <is>
           <t>天下秀</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr">
+      <c r="D187" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="7" t="n">
+      <c r="A188" s="10" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="7" t="inlineStr">
+      <c r="B188" s="10" t="inlineStr">
         <is>
           <t>600563</t>
         </is>
       </c>
-      <c r="C188" s="7" t="inlineStr">
+      <c r="C188" s="10" t="inlineStr">
         <is>
           <t>XD法拉电</t>
         </is>
       </c>
-      <c r="D188" s="7" t="inlineStr">
+      <c r="D188" s="10" t="inlineStr">
         <is>
           <t>L1-规则4:股价143.00&gt;100</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="7" t="n">
+      <c r="A189" s="10" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="B189" s="10" t="inlineStr">
         <is>
           <t>600565</t>
         </is>
       </c>
-      <c r="C189" s="7" t="inlineStr">
+      <c r="C189" s="10" t="inlineStr">
         <is>
           <t>ST迪马</t>
         </is>
       </c>
-      <c r="D189" s="7" t="inlineStr">
+      <c r="D189" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.85&lt;5</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="7" t="n">
+      <c r="A190" s="10" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="7" t="inlineStr">
+      <c r="B190" s="10" t="inlineStr">
         <is>
           <t>600567</t>
         </is>
       </c>
-      <c r="C190" s="7" t="inlineStr">
+      <c r="C190" s="10" t="inlineStr">
         <is>
           <t>山鹰国际</t>
         </is>
       </c>
-      <c r="D190" s="7" t="inlineStr">
+      <c r="D190" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.44&lt;5</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="7" t="n">
+      <c r="A191" s="10" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="7" t="inlineStr">
+      <c r="B191" s="10" t="inlineStr">
         <is>
           <t>600568</t>
         </is>
       </c>
-      <c r="C191" s="7" t="inlineStr">
+      <c r="C191" s="10" t="inlineStr">
         <is>
           <t>ST中珠</t>
         </is>
       </c>
-      <c r="D191" s="7" t="inlineStr">
+      <c r="D191" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.54&lt;5</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="7" t="n">
+      <c r="A192" s="10" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="7" t="inlineStr">
+      <c r="B192" s="10" t="inlineStr">
         <is>
           <t>600569</t>
         </is>
       </c>
-      <c r="C192" s="7" t="inlineStr">
+      <c r="C192" s="10" t="inlineStr">
         <is>
           <t>安阳钢铁</t>
         </is>
       </c>
-      <c r="D192" s="7" t="inlineStr">
+      <c r="D192" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价1.87&lt;5</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="7" t="n">
+      <c r="A193" s="10" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="7" t="inlineStr">
+      <c r="B193" s="10" t="inlineStr">
         <is>
           <t>600572</t>
         </is>
       </c>
-      <c r="C193" s="7" t="inlineStr">
+      <c r="C193" s="10" t="inlineStr">
         <is>
           <t>康恩贝</t>
         </is>
       </c>
-      <c r="D193" s="7" t="inlineStr">
+      <c r="D193" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="7" t="n">
+      <c r="A194" s="10" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B194" s="10" t="inlineStr">
         <is>
           <t>600575</t>
         </is>
       </c>
-      <c r="C194" s="7" t="inlineStr">
+      <c r="C194" s="10" t="inlineStr">
         <is>
           <t>淮河能源</t>
         </is>
       </c>
-      <c r="D194" s="7" t="inlineStr">
+      <c r="D194" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="7" t="n">
+      <c r="A195" s="10" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="B195" s="10" t="inlineStr">
         <is>
           <t>600576</t>
         </is>
       </c>
-      <c r="C195" s="7" t="inlineStr">
+      <c r="C195" s="10" t="inlineStr">
         <is>
           <t>祥源文旅</t>
         </is>
       </c>
-      <c r="D195" s="7" t="inlineStr">
+      <c r="D195" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="7" t="n">
+      <c r="A196" s="10" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="7" t="inlineStr">
+      <c r="B196" s="10" t="inlineStr">
         <is>
           <t>600581</t>
         </is>
       </c>
-      <c r="C196" s="7" t="inlineStr">
+      <c r="C196" s="10" t="inlineStr">
         <is>
           <t>*ST八钢</t>
         </is>
       </c>
-      <c r="D196" s="7" t="inlineStr">
+      <c r="D196" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价2.57&lt;5</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="7" t="n">
+      <c r="A197" s="10" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="B197" s="10" t="inlineStr">
         <is>
           <t>600586</t>
         </is>
       </c>
-      <c r="C197" s="7" t="inlineStr">
+      <c r="C197" s="10" t="inlineStr">
         <is>
           <t>金晶科技</t>
         </is>
       </c>
-      <c r="D197" s="7" t="inlineStr">
+      <c r="D197" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.57&lt;5</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="7" t="n">
+      <c r="A198" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="7" t="inlineStr">
+      <c r="B198" s="10" t="inlineStr">
         <is>
           <t>600594</t>
         </is>
       </c>
-      <c r="C198" s="7" t="inlineStr">
+      <c r="C198" s="10" t="inlineStr">
         <is>
           <t>益佰制药</t>
         </is>
       </c>
-      <c r="D198" s="7" t="inlineStr">
+      <c r="D198" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价3.29&lt;5</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="7" t="n">
+      <c r="A199" s="10" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B199" s="10" t="inlineStr">
         <is>
           <t>600599</t>
         </is>
       </c>
-      <c r="C199" s="7" t="inlineStr">
+      <c r="C199" s="10" t="inlineStr">
         <is>
           <t>退市熊猫</t>
         </is>
       </c>
-      <c r="D199" s="7" t="inlineStr">
+      <c r="D199" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="7" t="n">
+      <c r="A200" s="10" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="7" t="inlineStr">
+      <c r="B200" s="10" t="inlineStr">
         <is>
           <t>600601</t>
         </is>
       </c>
-      <c r="C200" s="7" t="inlineStr">
+      <c r="C200" s="10" t="inlineStr">
         <is>
           <t>方正科技</t>
         </is>
       </c>
-      <c r="D200" s="7" t="inlineStr">
+      <c r="D200" s="10" t="inlineStr">
         <is>
           <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="7" t="n">
+      <c r="A201" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="B201" s="10" t="inlineStr">
         <is>
           <t>600603</t>
         </is>
       </c>
-      <c r="C201" s="7" t="inlineStr">
+      <c r="C201" s="10" t="inlineStr">
         <is>
           <t>广汇物流</t>
         </is>
       </c>
-      <c r="D201" s="7" t="inlineStr">
+      <c r="D201" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.64&lt;5</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="7" t="n">
+      <c r="A202" s="10" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="7" t="inlineStr">
+      <c r="B202" s="10" t="inlineStr">
         <is>
           <t>600604</t>
         </is>
       </c>
-      <c r="C202" s="7" t="inlineStr">
+      <c r="C202" s="10" t="inlineStr">
         <is>
           <t>市北高新</t>
         </is>
       </c>
-      <c r="D202" s="7" t="inlineStr">
+      <c r="D202" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.22&lt;5</t>
         </is>
@@ -5234,68 +5478,68 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>信号过滤明细</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
+      <c r="B1" s="14" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>共触发信号过滤 4 项</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
+      <c r="B2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="11" t="n"/>
+      <c r="A3" s="14" t="n"/>
+      <c r="B3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>假动量高开</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>13次</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>缩量涨停</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>12次</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>诱多</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>10次</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>振幅&gt;15%</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>1次</t>
         </is>
@@ -5312,7 +5556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5326,44 +5570,140 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>策略</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>涨跌幅</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>量比</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>换手率</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>策略原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>600592</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>龙溪股份</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>跌5.2%(简版)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>600487</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>跌5.3%(简版)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>600234</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>科新发展</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>跌4.5%(简版)</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5392,44 +5732,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>策略</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>基础分</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>总分</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>置信度</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>预测逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>600592</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>龙溪股份</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>600487</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>600234</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>科新发展</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>B基础5; K线确认+1; ROE/CF数据不足; 信号-5; 新闻0</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5452,25 +5900,66 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>新闻筛查结果</t>
         </is>
       </c>
+      <c r="B1" s="14" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n"/>
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
+      <c r="A3" s="14" t="n"/>
+      <c r="B3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n"/>
+      <c r="A4" s="14" t="n"/>
+      <c r="B4" s="14" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>通过标的新闻备注:</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>600592 龙溪股份</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>通过(简化)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>600487 亨通光电</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>通过(简化)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>600234 科新发展</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>通过(简化)</t>
         </is>
       </c>
     </row>
@@ -5493,108 +5982,108 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>关键纪律 -- v6.5.1</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
+      <c r="B1" s="14" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>步骤零每次先于一切执行</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>网络授时北京时间优先</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>不追高</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>涨停(&gt;9.8%)/涨&gt;7%排除</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>同行业&lt;=3只</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>申万一级行业集中度控制</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>已持仓排除</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>7日内已推荐+已持仓排除</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>五级管道</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>硬排除31项-&gt;信号过滤14项-&gt;5策略-&gt;行业限制-&gt;新闻筛查</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>全市场API</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>东方财富clist一次性拉取，降级新浪API</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Excel格式化</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>openpyxl红涨绿跌+策略色+置信度色</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>仅供参考</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>不构成投资建议</t>
         </is>

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>龙溪股份</t>
+          <t>铜峰电子</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600592</t>
+          <t>600237</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-5.18</v>
+        <v>-5.54</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16.64</v>
+        <v>10.45</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15.56</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7.86</v>
+        <v>9.24</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>15.56</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>14.94</v>
+        <v>9.32</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>16.34</v>
+        <v>10.2</v>
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600592.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600237.html</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>安彩高科</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>600207</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-5.27</v>
+        <v>-5.61</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>105.08</v>
+        <v>6.47</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>97</v>
+        <v>6.06</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -773,17 +773,17 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>97</v>
+        <v>6.06</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>93.12</v>
+        <v>5.82</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>101.85</v>
+        <v>6.36</v>
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600487.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600207.html</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>科新发展</t>
+          <t>厦门钨业</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>600234</t>
+          <t>600549</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-4.5</v>
+        <v>-3.91</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25.57</v>
+        <v>69</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24.39</v>
+        <v>64.8</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>6.81</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -845,17 +845,17 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>24.39</v>
+        <v>64.8</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>23.41</v>
+        <v>62.21</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>25.61</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600234.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600549.html</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>201只</t>
+          <t>204只</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>14只</t>
+          <t>11只</t>
         </is>
       </c>
       <c r="C19" s="14" t="n"/>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D202"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2929,17 +2929,17 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>600238</t>
+          <t>600234</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>*ST椰岛</t>
+          <t>科新发展</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.91&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -2949,17 +2949,17 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>600239</t>
+          <t>600238</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>ST云城</t>
+          <t>*ST椰岛</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.42&lt;5</t>
+          <t>L1-规则3:股价4.91&lt;5</t>
         </is>
       </c>
     </row>
@@ -2969,17 +2969,17 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>600240</t>
+          <t>600239</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>退市华业</t>
+          <t>ST云城</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价1.42&lt;5</t>
         </is>
       </c>
     </row>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>600242</t>
+          <t>600240</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>退市中昌</t>
+          <t>退市华业</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.25&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>600243</t>
+          <t>600242</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>*ST海华</t>
+          <t>退市中昌</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.02&lt;5</t>
+          <t>L1-规则3:股价0.25&lt;5</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>600247</t>
+          <t>600243</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>*ST成城</t>
+          <t>*ST海华</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.65&lt;5</t>
+          <t>L1-规则3:股价4.02&lt;5</t>
         </is>
       </c>
     </row>
@@ -3049,17 +3049,17 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600247</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>陕建股份</t>
+          <t>*ST成城</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.02&lt;5</t>
+          <t>L1-规则3:股价0.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -3069,17 +3069,17 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>600252</t>
+          <t>600248</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>中恒集团</t>
+          <t>陕建股份</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.16&lt;5</t>
+          <t>L1-规则3:股价3.02&lt;5</t>
         </is>
       </c>
     </row>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>600255</t>
+          <t>600252</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>鑫科材料</t>
+          <t>中恒集团</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.15&lt;5</t>
+          <t>L1-规则3:股价2.16&lt;5</t>
         </is>
       </c>
     </row>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>600260</t>
+          <t>600255</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>*ST凯乐</t>
+          <t>鑫科材料</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.47&lt;5</t>
+          <t>L1-规则3:股价4.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>600261</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>*ST凯乐</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.19&lt;5</t>
+          <t>L1-规则3:股价0.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -3149,17 +3149,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>600265</t>
+          <t>600261</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>*ST景谷</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价3.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -3169,17 +3169,17 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>600266</t>
+          <t>600265</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>城建发展</t>
+          <t>*ST景谷</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.43&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3189,17 +3189,17 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>600269</t>
+          <t>600266</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>赣粤高速</t>
+          <t>城建发展</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.20&lt;5</t>
+          <t>L1-规则3:股价4.43&lt;5</t>
         </is>
       </c>
     </row>
@@ -3209,17 +3209,17 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>600275</t>
+          <t>600269</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>退市昌鱼</t>
+          <t>赣粤高速</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -3229,17 +3229,17 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>600277</t>
+          <t>600275</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>ST亿利</t>
+          <t>退市昌鱼</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.38&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3249,17 +3249,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>600279</t>
+          <t>600277</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>重庆港</t>
+          <t>ST亿利</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.44&lt;5</t>
+          <t>L1-规则3:股价0.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>600280</t>
+          <t>600279</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>中央商场</t>
+          <t>重庆港</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.93&lt;5</t>
+          <t>L1-规则3:股价4.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -3289,17 +3289,17 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>600281</t>
+          <t>600280</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>华阳新材</t>
+          <t>中央商场</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.90&lt;5</t>
+          <t>L1-规则3:股价2.93&lt;5</t>
         </is>
       </c>
     </row>
@@ -3309,17 +3309,17 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>600282</t>
+          <t>600281</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>南钢股份</t>
+          <t>华阳新材</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.84&lt;5</t>
+          <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>600287</t>
+          <t>600282</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>苏豪时尚</t>
+          <t>南钢股份</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.90&lt;5</t>
+          <t>L1-规则3:股价4.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -3349,17 +3349,17 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>600289</t>
+          <t>600287</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>ST信通</t>
+          <t>苏豪时尚</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3369,17 +3369,17 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>600290</t>
+          <t>600289</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>*ST华仪</t>
+          <t>ST信通</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3389,17 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>600291</t>
+          <t>600290</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>退市西水</t>
+          <t>*ST华仪</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.89&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3409,17 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>600292</t>
+          <t>600291</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>电投水电</t>
+          <t>退市西水</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价0.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -3429,17 +3429,17 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>600293</t>
+          <t>600292</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>电投水电</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.41&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>600297</t>
+          <t>600293</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>广汇汽车</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.78&lt;5</t>
+          <t>L1-规则3:股价3.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3469,17 +3469,17 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>600297</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>广汇汽车</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.07&lt;5</t>
+          <t>L1-规则3:股价0.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -3489,17 +3489,17 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>600301</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>华锡有色</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.6%&gt;7%</t>
+          <t>L1-规则3:股价3.07&lt;5</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3509,17 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>600302</t>
+          <t>600301</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>ST标准</t>
+          <t>华锡有色</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则12:涨幅7.6%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3529,17 +3529,17 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>600303</t>
+          <t>600302</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>曙光股份</t>
+          <t>ST标准</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.04&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3549,17 +3549,17 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>600306</t>
+          <t>600303</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>退市商城</t>
+          <t>曙光股份</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.29&lt;5</t>
+          <t>L1-规则3:股价3.04&lt;5</t>
         </is>
       </c>
     </row>
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>600307</t>
+          <t>600306</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>酒钢宏兴</t>
+          <t>退市商城</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.57&lt;5</t>
+          <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -3589,17 +3589,17 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>600308</t>
+          <t>600307</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>华泰股份</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.36&lt;5</t>
+          <t>L1-规则3:股价1.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3609,17 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>600310</t>
+          <t>600308</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>华泰股份</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.63&lt;5</t>
+          <t>L1-规则3:股价3.36&lt;5</t>
         </is>
       </c>
     </row>
@@ -3629,17 +3629,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>600311</t>
+          <t>600310</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>*ST荣华</t>
+          <t>广西能源</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.61&lt;5</t>
+          <t>L1-规则3:股价4.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3649,17 +3649,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>600317</t>
+          <t>600311</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>营口港</t>
+          <t>*ST荣华</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.60&lt;5</t>
+          <t>L1-规则3:股价0.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3669,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>600320</t>
+          <t>600317</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>振华重工</t>
+          <t>营口港</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价2.60&lt;5</t>
         </is>
       </c>
     </row>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>600321</t>
+          <t>600320</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>正源股份</t>
+          <t>振华重工</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.50&lt;5</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -3709,17 +3709,17 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>600322</t>
+          <t>600321</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>津投城开</t>
+          <t>正源股份</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.68&lt;5</t>
+          <t>L1-规则3:股价0.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>600325</t>
+          <t>600322</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>华发股份</t>
+          <t>津投城开</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.63&lt;5</t>
+          <t>L1-规则3:股价2.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -3749,17 +3749,17 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>600327</t>
+          <t>600325</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>大东方</t>
+          <t>华发股份</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价2.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3769,17 +3769,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>600337</t>
+          <t>600327</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>ST美克</t>
+          <t>大东方</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>600339</t>
+          <t>600337</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>中油工程</t>
+          <t>ST美克</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.31&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>600340</t>
+          <t>600339</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>*ST华幸</t>
+          <t>中油工程</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.33&lt;5</t>
+          <t>L1-规则3:股价3.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>600346</t>
+          <t>600340</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>恒力石化</t>
+          <t>*ST华幸</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价1.33&lt;5</t>
         </is>
       </c>
     </row>
@@ -3849,17 +3849,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>600355</t>
+          <t>600346</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>*ST精伦</t>
+          <t>恒力石化</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.58&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>600361</t>
+          <t>600355</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>创新新材</t>
+          <t>*ST精伦</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则3:股价0.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -3889,17 +3889,17 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>600362</t>
+          <t>600361</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>江西铜业</t>
+          <t>创新新材</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -3909,17 +3909,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>600365</t>
+          <t>600362</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>ST通葡</t>
+          <t>江西铜业</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.55&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>600368</t>
+          <t>600365</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>五洲交通</t>
+          <t>ST通葡</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.78&lt;5</t>
+          <t>L1-规则3:股价2.55&lt;5</t>
         </is>
       </c>
     </row>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>600369</t>
+          <t>600368</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>西南证券</t>
+          <t>五洲交通</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
+          <t>L1-规则3:股价3.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -3969,17 +3969,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>600370</t>
+          <t>600369</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>*ST三房</t>
+          <t>西南证券</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.46&lt;5</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>600375</t>
+          <t>600370</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>汉马科技</t>
+          <t>*ST三房</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.94&lt;5</t>
+          <t>L1-规则3:股价1.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -4009,17 +4009,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>600376</t>
+          <t>600375</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>首开股份</t>
+          <t>汉马科技</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.40&lt;5</t>
+          <t>L1-规则3:股价3.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -4029,17 +4029,17 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>600378</t>
+          <t>600376</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>XD昊华科</t>
+          <t>首开股份</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则3:股价3.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>600381</t>
+          <t>600378</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>*ST春天</t>
+          <t>XD昊华科</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -4069,17 +4069,17 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>600383</t>
+          <t>600381</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>金地集团</t>
+          <t>*ST春天</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.51&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4089,17 +4089,17 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>600385</t>
+          <t>600383</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>退市金泰</t>
+          <t>金地集团</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.20&lt;5</t>
+          <t>L1-规则3:股价2.51&lt;5</t>
         </is>
       </c>
     </row>
@@ -4109,17 +4109,17 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>600386</t>
+          <t>600385</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>北巴传媒</t>
+          <t>退市金泰</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价1.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -4129,17 +4129,17 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>600387</t>
+          <t>600386</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>退市海越</t>
+          <t>北巴传媒</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.94&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -4149,17 +4149,17 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>600390</t>
+          <t>600387</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>五矿资本</t>
+          <t>退市海越</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.65&lt;5</t>
+          <t>L1-规则3:股价0.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>600391</t>
+          <t>600390</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>航发科技</t>
+          <t>五矿资本</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -4189,17 +4189,17 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>600393</t>
+          <t>600391</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>ST粤泰</t>
+          <t>航发科技</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4209,17 +4209,17 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>600393</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>抚顺特钢</t>
+          <t>ST粤泰</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.32&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -4229,17 +4229,17 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>600400</t>
+          <t>600399</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>抚顺特钢</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.61&lt;5</t>
+          <t>L1-规则3:股价4.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -4249,17 +4249,17 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>600401</t>
+          <t>600400</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>退市海润</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.15&lt;5</t>
+          <t>L1-规则3:股价2.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -4269,17 +4269,17 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>600403</t>
+          <t>600401</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>大有能源</t>
+          <t>退市海润</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-9.9%</t>
+          <t>L1-规则3:股价0.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4289,17 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>600405</t>
+          <t>600403</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>动力源</t>
+          <t>大有能源</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.26&lt;5</t>
+          <t>L1-规则22:跌停-9.9%</t>
         </is>
       </c>
     </row>
@@ -4309,17 +4309,17 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>600408</t>
+          <t>600405</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>动力源</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.88&lt;5</t>
+          <t>L1-规则3:股价4.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4329,17 +4329,17 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>600421</t>
+          <t>600408</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>退市华嵘</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则3:股价2.88&lt;5</t>
         </is>
       </c>
     </row>
@@ -4349,17 +4349,17 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>600423</t>
+          <t>600421</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>*ST柳化</t>
+          <t>退市华嵘</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.48&lt;5</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>600425</t>
+          <t>600423</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>XD青松建</t>
+          <t>*ST柳化</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.54&lt;5</t>
+          <t>L1-规则3:股价2.48&lt;5</t>
         </is>
       </c>
     </row>
@@ -4389,17 +4389,17 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>600429</t>
+          <t>600425</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>三元股份</t>
+          <t>XD青松建</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价3.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -4409,17 +4409,17 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>600432</t>
+          <t>600429</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>退市吉恩</t>
+          <t>三元股份</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.38&lt;5</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4429,17 +4429,17 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>600433</t>
+          <t>600432</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>冠豪高新</t>
+          <t>退市吉恩</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.53&lt;5</t>
+          <t>L1-规则3:股价1.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -4449,17 +4449,17 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>600436</t>
+          <t>600433</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>片仔癀</t>
+          <t>冠豪高新</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价119.56&gt;100</t>
+          <t>L1-规则3:股价3.53&lt;5</t>
         </is>
       </c>
     </row>
@@ -4469,17 +4469,17 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>600439</t>
+          <t>600436</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>瑞贝卡</t>
+          <t>片仔癀</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.27&lt;5</t>
+          <t>L1-规则4:股价119.56&gt;100</t>
         </is>
       </c>
     </row>
@@ -4489,17 +4489,17 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>600448</t>
+          <t>600439</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>华纺股份</t>
+          <t>瑞贝卡</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则3:股价2.27&lt;5</t>
         </is>
       </c>
     </row>
@@ -4509,17 +4509,17 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>600462</t>
+          <t>600448</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>退市九有</t>
+          <t>华纺股份</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.21&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>600466</t>
+          <t>600462</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>*ST蓝光</t>
+          <t>退市九有</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.40&lt;5</t>
+          <t>L1-规则3:股价0.21&lt;5</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>600467</t>
+          <t>600466</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>好当家</t>
+          <t>*ST蓝光</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则3:股价0.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>600476</t>
+          <t>600467</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>*ST湘邮</t>
+          <t>好当家</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -4589,17 +4589,17 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>600477</t>
+          <t>600476</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>杭萧钢构</t>
+          <t>*ST湘邮</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.59&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4609,17 +4609,17 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>600485</t>
+          <t>600477</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>*ST信威</t>
+          <t>杭萧钢构</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.39&lt;5</t>
+          <t>L1-规则3:股价2.59&lt;5</t>
         </is>
       </c>
     </row>
@@ -4629,17 +4629,17 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>600488</t>
+          <t>600485</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>*ST信威</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.76&lt;5</t>
+          <t>L1-规则3:股价1.39&lt;5</t>
         </is>
       </c>
     </row>
@@ -4649,17 +4649,17 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>600491</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>ST龙元</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.31&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -4669,17 +4669,17 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>600495</t>
+          <t>600488</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>晋西车轴</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.80&lt;5</t>
+          <t>L1-规则3:股价4.76&lt;5</t>
         </is>
       </c>
     </row>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>600496</t>
+          <t>600491</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>精工钢构</t>
+          <t>ST龙元</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.84&lt;5</t>
+          <t>L1-规则3:股价1.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -4709,17 +4709,17 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>600497</t>
+          <t>600495</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>驰宏锌锗</t>
+          <t>晋西车轴</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停9.9%</t>
+          <t>L1-规则3:股价3.80&lt;5</t>
         </is>
       </c>
     </row>
@@ -4729,17 +4729,17 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>600500</t>
+          <t>600496</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>中化国际</t>
+          <t>精工钢构</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价3.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4749,17 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>600502</t>
+          <t>600497</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>安徽建工</t>
+          <t>驰宏锌锗</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.68&lt;5</t>
+          <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
@@ -4769,17 +4769,17 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>600503</t>
+          <t>600500</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>中化国际</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.46&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4789,17 +4789,17 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>600507</t>
+          <t>600502</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>方大特钢</t>
+          <t>安徽建工</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.29&lt;5</t>
+          <t>L1-规则3:股价4.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -4809,17 +4809,17 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>600512</t>
+          <t>600503</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>腾达建设</t>
+          <t>华丽家族</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.08&lt;5</t>
+          <t>L1-规则3:股价2.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -4829,17 +4829,17 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>600515</t>
+          <t>600507</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>海南机场</t>
+          <t>方大特钢</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.98&lt;5</t>
+          <t>L1-规则3:股价4.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -4849,17 +4849,17 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>600517</t>
+          <t>600512</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>国网英大</t>
+          <t>腾达建设</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则3:股价2.08&lt;5</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>600518</t>
+          <t>600515</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>康美药业</t>
+          <t>海南机场</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.40&lt;5</t>
+          <t>L1-规则3:股价2.98&lt;5</t>
         </is>
       </c>
     </row>
@@ -4889,17 +4889,17 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600517</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>国网英大</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价1291.91&gt;100</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -4909,17 +4909,17 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>600525</t>
+          <t>600518</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>康美药业</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.99&lt;5</t>
+          <t>L1-规则3:股价1.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>600526</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>菲达环保</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.49&lt;5</t>
+          <t>L1-规则4:股价1291.91&gt;100</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4949,17 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>600527</t>
+          <t>600525</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>江南高纤</t>
+          <t>ST长园</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.32&lt;5</t>
+          <t>L1-规则3:股价4.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>600531</t>
+          <t>600526</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>豫光金铅</t>
+          <t>菲达环保</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.49&lt;5</t>
         </is>
       </c>
     </row>
@@ -4989,17 +4989,17 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>600532</t>
+          <t>600527</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>退市未来</t>
+          <t>江南高纤</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.72&lt;5</t>
+          <t>L1-规则3:股价2.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -5009,17 +5009,17 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>600533</t>
+          <t>600531</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>栖霞建设</t>
+          <t>豫光金铅</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5029,17 +5029,17 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>600536</t>
+          <t>600532</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>中国软件</t>
+          <t>退市未来</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则3:股价0.72&lt;5</t>
         </is>
       </c>
     </row>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>600537</t>
+          <t>600533</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>*ST亿晶</t>
+          <t>栖霞建设</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.58&lt;5</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5069,17 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>600539</t>
+          <t>600536</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>狮头股份</t>
+          <t>中国软件</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -5089,17 +5089,17 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>600540</t>
+          <t>600537</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>新赛股份</t>
+          <t>*ST亿晶</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.46&lt;5</t>
+          <t>L1-规则3:股价2.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -5109,17 +5109,17 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>600543</t>
+          <t>600539</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>*ST莫高</t>
+          <t>狮头股份</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.22&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5129,17 +5129,17 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>600555</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>退市海创</t>
+          <t>新赛股份</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则3:股价4.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5149,17 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>600556</t>
+          <t>600543</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>天下秀</t>
+          <t>*ST莫高</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则3:股价4.22&lt;5</t>
         </is>
       </c>
     </row>
@@ -5169,17 +5169,17 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>600563</t>
+          <t>600555</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>XD法拉电</t>
+          <t>退市海创</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价143.00&gt;100</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5189,17 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>600565</t>
+          <t>600556</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>ST迪马</t>
+          <t>天下秀</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.85&lt;5</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -5209,17 +5209,17 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>600567</t>
+          <t>600563</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>山鹰国际</t>
+          <t>XD法拉电</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.44&lt;5</t>
+          <t>L1-规则4:股价143.00&gt;100</t>
         </is>
       </c>
     </row>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>600568</t>
+          <t>600565</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>ST中珠</t>
+          <t>ST迪马</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.54&lt;5</t>
+          <t>L1-规则3:股价0.85&lt;5</t>
         </is>
       </c>
     </row>
@@ -5249,17 +5249,17 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>600569</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>安阳钢铁</t>
+          <t>山鹰国际</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.87&lt;5</t>
+          <t>L1-规则3:股价1.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -5269,17 +5269,17 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>600572</t>
+          <t>600568</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>康恩贝</t>
+          <t>ST中珠</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则3:股价2.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -5289,17 +5289,17 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>600575</t>
+          <t>600569</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>淮河能源</t>
+          <t>安阳钢铁</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
+          <t>L1-规则3:股价1.87&lt;5</t>
         </is>
       </c>
     </row>
@@ -5309,17 +5309,17 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>600576</t>
+          <t>600572</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>祥源文旅</t>
+          <t>康恩贝</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -5329,17 +5329,17 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>600581</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>*ST八钢</t>
+          <t>淮河能源</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.57&lt;5</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -5349,17 +5349,17 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>600586</t>
+          <t>600576</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>金晶科技</t>
+          <t>祥源文旅</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.57&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>600594</t>
+          <t>600581</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>益佰制药</t>
+          <t>*ST八钢</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.29&lt;5</t>
+          <t>L1-规则3:股价2.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>600599</t>
+          <t>600586</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>退市熊猫</t>
+          <t>金晶科技</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5409,17 +5409,17 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>600601</t>
+          <t>600592</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>方正科技</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -5429,17 +5429,17 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>600603</t>
+          <t>600594</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>广汇物流</t>
+          <t>益佰制药</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.64&lt;5</t>
+          <t>L1-规则3:股价3.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -5449,15 +5449,75 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
+          <t>600599</t>
+        </is>
+      </c>
+      <c r="C202" s="10" t="inlineStr">
+        <is>
+          <t>退市熊猫</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="10" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
+        <is>
+          <t>600601</t>
+        </is>
+      </c>
+      <c r="C203" s="10" t="inlineStr">
+        <is>
+          <t>方正科技</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="10" t="inlineStr">
+        <is>
+          <t>600603</t>
+        </is>
+      </c>
+      <c r="C204" s="10" t="inlineStr">
+        <is>
+          <t>广汇物流</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.64&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="10" t="inlineStr">
+        <is>
           <t>600604</t>
         </is>
       </c>
-      <c r="C202" s="10" t="inlineStr">
+      <c r="C205" s="10" t="inlineStr">
         <is>
           <t>市北高新</t>
         </is>
       </c>
-      <c r="D202" s="10" t="inlineStr">
+      <c r="D205" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.22&lt;5</t>
         </is>
@@ -5617,12 +5677,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600592</t>
+          <t>600237</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>龙溪股份</t>
+          <t>铜峰电子</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5631,7 +5691,7 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>-5.18</v>
+        <v>-5.54</v>
       </c>
       <c r="F2" s="10" t="n"/>
       <c r="G2" s="10" t="n">
@@ -5639,7 +5699,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>跌5.2%(简版)</t>
+          <t>跌5.5%(简版)</t>
         </is>
       </c>
     </row>
@@ -5649,12 +5709,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>600207</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>安彩高科</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5663,7 +5723,7 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-5.27</v>
+        <v>-5.61</v>
       </c>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n">
@@ -5671,7 +5731,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>跌5.3%(简版)</t>
+          <t>跌5.6%(简版)</t>
         </is>
       </c>
     </row>
@@ -5681,12 +5741,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600234</t>
+          <t>600549</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>科新发展</t>
+          <t>厦门钨业</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5695,7 +5755,7 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-4.5</v>
+        <v>-3.91</v>
       </c>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n">
@@ -5703,7 +5763,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>跌4.5%(简版)</t>
+          <t>跌3.9%(简版)</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5839,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600592</t>
+          <t>600237</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>龙溪股份</t>
+          <t>铜峰电子</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5815,12 +5875,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>600207</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>安彩高科</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5851,12 +5911,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600234</t>
+          <t>600549</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>科新发展</t>
+          <t>厦门钨业</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5930,7 +5990,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>600592 龙溪股份</t>
+          <t>600237 铜峰电子</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -5942,7 +6002,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>600487 亨通光电</t>
+          <t>600207 安彩高科</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -5954,7 +6014,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>600234 科新发展</t>
+          <t>600549 厦门钨业</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>铜峰电子</t>
+          <t>万通发展</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600237</t>
+          <t>600246</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-5.54</v>
+        <v>-6.24</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.45</v>
+        <v>17.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>16.07</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>9.24</v>
+        <v>10.44</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>16.07</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>9.32</v>
+        <v>15.43</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>10.2</v>
+        <v>16.87</v>
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600237.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600246.html</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>安彩高科</t>
+          <t>京能电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600207</t>
+          <t>600578</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-5.61</v>
+        <v>-3.73</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>6.47</v>
+        <v>7.8</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6.06</v>
+        <v>7.49</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>9.81</v>
+        <v>6.04</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -773,17 +773,17 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>6.06</v>
+        <v>7.49</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>5.82</v>
+        <v>7.19</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>6.36</v>
+        <v>7.86</v>
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600207.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600578.html</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>厦门钨业</t>
+          <t>天通股份</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>600549</t>
+          <t>600330</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-3.91</v>
+        <v>-3.62</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>69</v>
+        <v>30.09</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>64.8</v>
+        <v>28.25</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -845,17 +845,17 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>64.8</v>
+        <v>28.25</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>62.21</v>
+        <v>27.12</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>68.04000000000001</v>
+        <v>29.66</v>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600549.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600330.html</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>204只</t>
+          <t>207只</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>11只</t>
+          <t>8只</t>
         </is>
       </c>
       <c r="C19" s="14" t="n"/>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2709,17 +2709,17 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>600208</t>
+          <t>600207</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>衢州发展</t>
+          <t>安彩高科</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.97&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -2729,17 +2729,17 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>600209</t>
+          <t>600208</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>退市罗顿</t>
+          <t>衢州发展</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.18&lt;5</t>
+          <t>L1-规则3:股价2.97&lt;5</t>
         </is>
       </c>
     </row>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>600213</t>
+          <t>600209</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>*ST亚星</t>
+          <t>退市罗顿</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价1.18&lt;5</t>
         </is>
       </c>
     </row>
@@ -2769,17 +2769,17 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>600217</t>
+          <t>600213</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>中再资环</t>
+          <t>*ST亚星</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.15&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -2789,17 +2789,17 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>600219</t>
+          <t>600217</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>中再资环</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.73&lt;5</t>
+          <t>L1-规则3:股价3.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -2809,17 +2809,17 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>600220</t>
+          <t>600219</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>ST阳光</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则3:股价4.73&lt;5</t>
         </is>
       </c>
     </row>
@@ -2829,17 +2829,17 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>600221</t>
+          <t>600220</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>海航控股</t>
+          <t>ST阳光</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.53&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -2849,17 +2849,17 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>600225</t>
+          <t>600221</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>退市卓朗</t>
+          <t>海航控股</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.29&lt;5</t>
+          <t>L1-规则3:股价1.53&lt;5</t>
         </is>
       </c>
     </row>
@@ -2869,17 +2869,17 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>600227</t>
+          <t>600225</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>赤天化</t>
+          <t>退市卓朗</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.87&lt;5</t>
+          <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>600229</t>
+          <t>600227</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>城市传媒</t>
+          <t>赤天化</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停9.9%</t>
+          <t>L1-规则3:股价2.87&lt;5</t>
         </is>
       </c>
     </row>
@@ -2909,17 +2909,17 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>600231</t>
+          <t>600229</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>凌钢股份</t>
+          <t>城市传媒</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.89&lt;5</t>
+          <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
@@ -2929,17 +2929,17 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>600234</t>
+          <t>600231</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>科新发展</t>
+          <t>凌钢股份</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价1.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -2949,17 +2949,17 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>600238</t>
+          <t>600234</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>*ST椰岛</t>
+          <t>科新发展</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.91&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -2969,17 +2969,17 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>600239</t>
+          <t>600237</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>ST云城</t>
+          <t>铜峰电子</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.42&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>600240</t>
+          <t>600238</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>退市华业</t>
+          <t>*ST椰岛</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.91&lt;5</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>600242</t>
+          <t>600239</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>退市中昌</t>
+          <t>ST云城</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.25&lt;5</t>
+          <t>L1-规则3:股价1.42&lt;5</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>600243</t>
+          <t>600240</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>*ST海华</t>
+          <t>退市华业</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.02&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3049,17 +3049,17 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>600247</t>
+          <t>600242</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>*ST成城</t>
+          <t>退市中昌</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.65&lt;5</t>
+          <t>L1-规则3:股价0.25&lt;5</t>
         </is>
       </c>
     </row>
@@ -3069,17 +3069,17 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600243</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>陕建股份</t>
+          <t>*ST海华</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.02&lt;5</t>
+          <t>L1-规则3:股价4.02&lt;5</t>
         </is>
       </c>
     </row>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>600252</t>
+          <t>600247</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>中恒集团</t>
+          <t>*ST成城</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.16&lt;5</t>
+          <t>L1-规则3:股价0.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>600255</t>
+          <t>600248</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>鑫科材料</t>
+          <t>陕建股份</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.15&lt;5</t>
+          <t>L1-规则3:股价3.02&lt;5</t>
         </is>
       </c>
     </row>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>600260</t>
+          <t>600252</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>*ST凯乐</t>
+          <t>中恒集团</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.47&lt;5</t>
+          <t>L1-规则3:股价2.16&lt;5</t>
         </is>
       </c>
     </row>
@@ -3149,17 +3149,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>600261</t>
+          <t>600255</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>鑫科材料</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.19&lt;5</t>
+          <t>L1-规则3:股价4.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -3169,17 +3169,17 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>600265</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>*ST景谷</t>
+          <t>*ST凯乐</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价0.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -3189,17 +3189,17 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>600266</t>
+          <t>600261</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>城建发展</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.43&lt;5</t>
+          <t>L1-规则3:股价3.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -3209,17 +3209,17 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>600269</t>
+          <t>600265</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>赣粤高速</t>
+          <t>*ST景谷</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.20&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3229,17 +3229,17 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>600275</t>
+          <t>600266</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>退市昌鱼</t>
+          <t>城建发展</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.43&lt;5</t>
         </is>
       </c>
     </row>
@@ -3249,17 +3249,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>600277</t>
+          <t>600269</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>ST亿利</t>
+          <t>赣粤高速</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.38&lt;5</t>
+          <t>L1-规则3:股价4.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>600279</t>
+          <t>600275</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>重庆港</t>
+          <t>退市昌鱼</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.44&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3289,17 +3289,17 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>600280</t>
+          <t>600277</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>中央商场</t>
+          <t>ST亿利</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.93&lt;5</t>
+          <t>L1-规则3:股价0.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -3309,17 +3309,17 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>600281</t>
+          <t>600279</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>华阳新材</t>
+          <t>重庆港</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.90&lt;5</t>
+          <t>L1-规则3:股价4.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>600282</t>
+          <t>600280</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>南钢股份</t>
+          <t>中央商场</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.84&lt;5</t>
+          <t>L1-规则3:股价2.93&lt;5</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>600287</t>
+          <t>600281</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>苏豪时尚</t>
+          <t>华阳新材</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>600289</t>
+          <t>600282</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>ST信通</t>
+          <t>南钢股份</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价4.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3389,17 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>600290</t>
+          <t>600287</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>*ST华仪</t>
+          <t>苏豪时尚</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3409,17 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>600291</t>
+          <t>600289</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>退市西水</t>
+          <t>ST信通</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.89&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3429,17 +3429,17 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>600292</t>
+          <t>600290</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>电投水电</t>
+          <t>*ST华仪</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>600293</t>
+          <t>600291</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>退市西水</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.41&lt;5</t>
+          <t>L1-规则3:股价0.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -3469,17 +3469,17 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>600297</t>
+          <t>600292</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>广汇汽车</t>
+          <t>电投水电</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.78&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -3489,17 +3489,17 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>600293</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.07&lt;5</t>
+          <t>L1-规则3:股价3.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3509,17 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>600301</t>
+          <t>600297</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>华锡有色</t>
+          <t>广汇汽车</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.6%&gt;7%</t>
+          <t>L1-规则3:股价0.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -3529,17 +3529,17 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>600302</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>ST标准</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价3.07&lt;5</t>
         </is>
       </c>
     </row>
@@ -3549,17 +3549,17 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>600303</t>
+          <t>600301</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>曙光股份</t>
+          <t>华锡有色</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.04&lt;5</t>
+          <t>L1-规则12:涨幅7.6%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>600306</t>
+          <t>600302</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>退市商城</t>
+          <t>ST标准</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.29&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3589,17 +3589,17 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>600307</t>
+          <t>600303</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>酒钢宏兴</t>
+          <t>曙光股份</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.57&lt;5</t>
+          <t>L1-规则3:股价3.04&lt;5</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3609,17 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>600308</t>
+          <t>600306</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>华泰股份</t>
+          <t>退市商城</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.36&lt;5</t>
+          <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -3629,17 +3629,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>600310</t>
+          <t>600307</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.63&lt;5</t>
+          <t>L1-规则3:股价1.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -3649,17 +3649,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>600311</t>
+          <t>600308</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>*ST荣华</t>
+          <t>华泰股份</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.61&lt;5</t>
+          <t>L1-规则3:股价3.36&lt;5</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3669,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>600317</t>
+          <t>600310</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>营口港</t>
+          <t>广西能源</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.60&lt;5</t>
+          <t>L1-规则3:股价4.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>600320</t>
+          <t>600311</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>振华重工</t>
+          <t>*ST荣华</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价0.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -3709,17 +3709,17 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>600321</t>
+          <t>600317</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>正源股份</t>
+          <t>营口港</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.50&lt;5</t>
+          <t>L1-规则3:股价2.60&lt;5</t>
         </is>
       </c>
     </row>
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>600322</t>
+          <t>600320</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>津投城开</t>
+          <t>振华重工</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.68&lt;5</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -3749,17 +3749,17 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>600325</t>
+          <t>600321</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>华发股份</t>
+          <t>正源股份</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.63&lt;5</t>
+          <t>L1-规则3:股价0.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3769,17 +3769,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>600327</t>
+          <t>600322</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>大东方</t>
+          <t>津投城开</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价2.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>600337</t>
+          <t>600325</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>ST美克</t>
+          <t>华发股份</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则3:股价2.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>600339</t>
+          <t>600327</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>中油工程</t>
+          <t>大东方</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.31&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>600340</t>
+          <t>600337</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>*ST华幸</t>
+          <t>ST美克</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.33&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3849,17 +3849,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>600346</t>
+          <t>600339</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>恒力石化</t>
+          <t>中油工程</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价3.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>600355</t>
+          <t>600340</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>*ST精伦</t>
+          <t>*ST华幸</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.58&lt;5</t>
+          <t>L1-规则3:股价1.33&lt;5</t>
         </is>
       </c>
     </row>
@@ -3889,17 +3889,17 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>600361</t>
+          <t>600346</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>创新新材</t>
+          <t>恒力石化</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3909,17 +3909,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>600362</t>
+          <t>600355</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>江西铜业</t>
+          <t>*ST精伦</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价0.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>600365</t>
+          <t>600361</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>ST通葡</t>
+          <t>创新新材</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.55&lt;5</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>600368</t>
+          <t>600362</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>五洲交通</t>
+          <t>江西铜业</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.78&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3969,17 +3969,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>600369</t>
+          <t>600365</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>西南证券</t>
+          <t>ST通葡</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
+          <t>L1-规则3:股价2.55&lt;5</t>
         </is>
       </c>
     </row>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>600370</t>
+          <t>600368</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>*ST三房</t>
+          <t>五洲交通</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.46&lt;5</t>
+          <t>L1-规则3:股价3.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -4009,17 +4009,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>600375</t>
+          <t>600369</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>汉马科技</t>
+          <t>西南证券</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.94&lt;5</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -4029,17 +4029,17 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>600376</t>
+          <t>600370</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>首开股份</t>
+          <t>*ST三房</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.40&lt;5</t>
+          <t>L1-规则3:股价1.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>600378</t>
+          <t>600375</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>XD昊华科</t>
+          <t>汉马科技</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则3:股价3.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -4069,17 +4069,17 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>600381</t>
+          <t>600376</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>*ST春天</t>
+          <t>首开股份</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价3.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4089,17 +4089,17 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>600383</t>
+          <t>600378</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>金地集团</t>
+          <t>XD昊华科</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.51&lt;5</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -4109,17 +4109,17 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>600385</t>
+          <t>600381</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>退市金泰</t>
+          <t>*ST春天</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.20&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4129,17 +4129,17 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>600386</t>
+          <t>600383</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>北巴传媒</t>
+          <t>金地集团</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价2.51&lt;5</t>
         </is>
       </c>
     </row>
@@ -4149,17 +4149,17 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>600387</t>
+          <t>600385</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>退市海越</t>
+          <t>退市金泰</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.94&lt;5</t>
+          <t>L1-规则3:股价1.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>600390</t>
+          <t>600386</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>五矿资本</t>
+          <t>北巴传媒</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.65&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -4189,17 +4189,17 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>600391</t>
+          <t>600387</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>航发科技</t>
+          <t>退市海越</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价0.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -4209,17 +4209,17 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>600393</t>
+          <t>600390</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>ST粤泰</t>
+          <t>五矿资本</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则3:股价4.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -4229,17 +4229,17 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>600391</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>抚顺特钢</t>
+          <t>航发科技</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.32&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4249,17 +4249,17 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>600400</t>
+          <t>600393</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>ST粤泰</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.61&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -4269,17 +4269,17 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>600401</t>
+          <t>600399</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>退市海润</t>
+          <t>抚顺特钢</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.15&lt;5</t>
+          <t>L1-规则3:股价4.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4289,17 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>600403</t>
+          <t>600400</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>大有能源</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-9.9%</t>
+          <t>L1-规则3:股价2.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -4309,17 +4309,17 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>600405</t>
+          <t>600401</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>动力源</t>
+          <t>退市海润</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.26&lt;5</t>
+          <t>L1-规则3:股价0.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -4329,17 +4329,17 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>600408</t>
+          <t>600403</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>大有能源</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.88&lt;5</t>
+          <t>L1-规则22:跌停-9.9%</t>
         </is>
       </c>
     </row>
@@ -4349,17 +4349,17 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>600421</t>
+          <t>600405</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>退市华嵘</t>
+          <t>动力源</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则3:股价4.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>600423</t>
+          <t>600408</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>*ST柳化</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.48&lt;5</t>
+          <t>L1-规则3:股价2.88&lt;5</t>
         </is>
       </c>
     </row>
@@ -4389,17 +4389,17 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>600425</t>
+          <t>600421</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>XD青松建</t>
+          <t>退市华嵘</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.54&lt;5</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4409,17 +4409,17 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>600429</t>
+          <t>600423</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>三元股份</t>
+          <t>*ST柳化</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价2.48&lt;5</t>
         </is>
       </c>
     </row>
@@ -4429,17 +4429,17 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>600432</t>
+          <t>600425</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>退市吉恩</t>
+          <t>XD青松建</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.38&lt;5</t>
+          <t>L1-规则3:股价3.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -4449,17 +4449,17 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>600433</t>
+          <t>600429</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>冠豪高新</t>
+          <t>三元股份</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.53&lt;5</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4469,17 +4469,17 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>600436</t>
+          <t>600432</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>片仔癀</t>
+          <t>退市吉恩</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价119.56&gt;100</t>
+          <t>L1-规则3:股价1.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -4489,17 +4489,17 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>600439</t>
+          <t>600433</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>瑞贝卡</t>
+          <t>冠豪高新</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.27&lt;5</t>
+          <t>L1-规则3:股价3.53&lt;5</t>
         </is>
       </c>
     </row>
@@ -4509,17 +4509,17 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>600448</t>
+          <t>600436</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>华纺股份</t>
+          <t>片仔癀</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则4:股价119.56&gt;100</t>
         </is>
       </c>
     </row>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>600462</t>
+          <t>600439</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>退市九有</t>
+          <t>瑞贝卡</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.21&lt;5</t>
+          <t>L1-规则3:股价2.27&lt;5</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>600466</t>
+          <t>600448</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>*ST蓝光</t>
+          <t>华纺股份</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.40&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>600467</t>
+          <t>600462</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>好当家</t>
+          <t>退市九有</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则3:股价0.21&lt;5</t>
         </is>
       </c>
     </row>
@@ -4589,17 +4589,17 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>600476</t>
+          <t>600466</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>*ST湘邮</t>
+          <t>*ST蓝光</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价0.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4609,17 +4609,17 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>600477</t>
+          <t>600467</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>杭萧钢构</t>
+          <t>好当家</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.59&lt;5</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -4629,17 +4629,17 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>600485</t>
+          <t>600476</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>*ST信威</t>
+          <t>*ST湘邮</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.39&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4649,17 +4649,17 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>600477</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>杭萧钢构</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价2.59&lt;5</t>
         </is>
       </c>
     </row>
@@ -4669,17 +4669,17 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>600488</t>
+          <t>600485</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>*ST信威</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.76&lt;5</t>
+          <t>L1-规则3:股价1.39&lt;5</t>
         </is>
       </c>
     </row>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>600491</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>ST龙元</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.31&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -4709,17 +4709,17 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>600495</t>
+          <t>600488</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>晋西车轴</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.80&lt;5</t>
+          <t>L1-规则3:股价4.76&lt;5</t>
         </is>
       </c>
     </row>
@@ -4729,17 +4729,17 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>600496</t>
+          <t>600491</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>精工钢构</t>
+          <t>ST龙元</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.84&lt;5</t>
+          <t>L1-规则3:股价1.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4749,17 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>600497</t>
+          <t>600495</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>驰宏锌锗</t>
+          <t>晋西车轴</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停9.9%</t>
+          <t>L1-规则3:股价3.80&lt;5</t>
         </is>
       </c>
     </row>
@@ -4769,17 +4769,17 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>600500</t>
+          <t>600496</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>中化国际</t>
+          <t>精工钢构</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价3.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -4789,17 +4789,17 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>600502</t>
+          <t>600497</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>安徽建工</t>
+          <t>驰宏锌锗</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.68&lt;5</t>
+          <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
@@ -4809,17 +4809,17 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>600503</t>
+          <t>600500</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>中化国际</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.46&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4829,17 +4829,17 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>600507</t>
+          <t>600502</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>方大特钢</t>
+          <t>安徽建工</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.29&lt;5</t>
+          <t>L1-规则3:股价4.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -4849,17 +4849,17 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>600512</t>
+          <t>600503</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>腾达建设</t>
+          <t>华丽家族</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.08&lt;5</t>
+          <t>L1-规则3:股价2.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>600515</t>
+          <t>600507</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>海南机场</t>
+          <t>方大特钢</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.98&lt;5</t>
+          <t>L1-规则3:股价4.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -4889,17 +4889,17 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>600517</t>
+          <t>600512</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>国网英大</t>
+          <t>腾达建设</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则3:股价2.08&lt;5</t>
         </is>
       </c>
     </row>
@@ -4909,17 +4909,17 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>600518</t>
+          <t>600515</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>康美药业</t>
+          <t>海南机场</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.40&lt;5</t>
+          <t>L1-规则3:股价2.98&lt;5</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600517</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>国网英大</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价1291.91&gt;100</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4949,17 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>600525</t>
+          <t>600518</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>康美药业</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.99&lt;5</t>
+          <t>L1-规则3:股价1.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>600526</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>菲达环保</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.49&lt;5</t>
+          <t>L1-规则4:股价1291.91&gt;100</t>
         </is>
       </c>
     </row>
@@ -4989,17 +4989,17 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>600527</t>
+          <t>600525</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>江南高纤</t>
+          <t>ST长园</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.32&lt;5</t>
+          <t>L1-规则3:股价4.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -5009,17 +5009,17 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>600531</t>
+          <t>600526</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>豫光金铅</t>
+          <t>菲达环保</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.49&lt;5</t>
         </is>
       </c>
     </row>
@@ -5029,17 +5029,17 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>600532</t>
+          <t>600527</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>退市未来</t>
+          <t>江南高纤</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.72&lt;5</t>
+          <t>L1-规则3:股价2.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>600533</t>
+          <t>600531</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>栖霞建设</t>
+          <t>豫光金铅</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5069,17 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>600536</t>
+          <t>600532</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>中国软件</t>
+          <t>退市未来</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则3:股价0.72&lt;5</t>
         </is>
       </c>
     </row>
@@ -5089,17 +5089,17 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>600537</t>
+          <t>600533</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>*ST亿晶</t>
+          <t>栖霞建设</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.58&lt;5</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -5109,17 +5109,17 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>600539</t>
+          <t>600536</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>狮头股份</t>
+          <t>中国软件</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -5129,17 +5129,17 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>600540</t>
+          <t>600537</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>新赛股份</t>
+          <t>*ST亿晶</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.46&lt;5</t>
+          <t>L1-规则3:股价2.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5149,17 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>600543</t>
+          <t>600539</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>*ST莫高</t>
+          <t>狮头股份</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.22&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5169,17 +5169,17 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>600555</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>退市海创</t>
+          <t>新赛股份</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则3:股价4.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5189,17 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>600556</t>
+          <t>600543</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>天下秀</t>
+          <t>*ST莫高</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则3:股价4.22&lt;5</t>
         </is>
       </c>
     </row>
@@ -5209,17 +5209,17 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>600563</t>
+          <t>600549</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>XD法拉电</t>
+          <t>厦门钨业</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价143.00&gt;100</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>600565</t>
+          <t>600555</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>ST迪马</t>
+          <t>退市海创</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.85&lt;5</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -5249,17 +5249,17 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>600567</t>
+          <t>600556</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>山鹰国际</t>
+          <t>天下秀</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.44&lt;5</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -5269,17 +5269,17 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>600568</t>
+          <t>600563</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>ST中珠</t>
+          <t>XD法拉电</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.54&lt;5</t>
+          <t>L1-规则4:股价143.00&gt;100</t>
         </is>
       </c>
     </row>
@@ -5289,17 +5289,17 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>600569</t>
+          <t>600565</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>安阳钢铁</t>
+          <t>ST迪马</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.87&lt;5</t>
+          <t>L1-规则3:股价0.85&lt;5</t>
         </is>
       </c>
     </row>
@@ -5309,17 +5309,17 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>600572</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>康恩贝</t>
+          <t>山鹰国际</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则3:股价1.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -5329,17 +5329,17 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>600575</t>
+          <t>600568</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>淮河能源</t>
+          <t>ST中珠</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
+          <t>L1-规则3:股价2.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -5349,17 +5349,17 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>600576</t>
+          <t>600569</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>祥源文旅</t>
+          <t>安阳钢铁</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价1.87&lt;5</t>
         </is>
       </c>
     </row>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>600581</t>
+          <t>600572</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>*ST八钢</t>
+          <t>康恩贝</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.57&lt;5</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>600586</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>金晶科技</t>
+          <t>淮河能源</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.57&lt;5</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -5409,17 +5409,17 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>600592</t>
+          <t>600576</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>龙溪股份</t>
+          <t>祥源文旅</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5429,17 +5429,17 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>600594</t>
+          <t>600581</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>益佰制药</t>
+          <t>*ST八钢</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.29&lt;5</t>
+          <t>L1-规则3:股价2.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5449,17 +5449,17 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>600599</t>
+          <t>600586</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>退市熊猫</t>
+          <t>金晶科技</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5469,17 +5469,17 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>600601</t>
+          <t>600592</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>方正科技</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -5489,17 +5489,17 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>600603</t>
+          <t>600594</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>广汇物流</t>
+          <t>益佰制药</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.64&lt;5</t>
+          <t>L1-规则3:股价3.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -5509,15 +5509,75 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
+          <t>600599</t>
+        </is>
+      </c>
+      <c r="C205" s="10" t="inlineStr">
+        <is>
+          <t>退市熊猫</t>
+        </is>
+      </c>
+      <c r="D205" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>600601</t>
+        </is>
+      </c>
+      <c r="C206" s="10" t="inlineStr">
+        <is>
+          <t>方正科技</t>
+        </is>
+      </c>
+      <c r="D206" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="10" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="10" t="inlineStr">
+        <is>
+          <t>600603</t>
+        </is>
+      </c>
+      <c r="C207" s="10" t="inlineStr">
+        <is>
+          <t>广汇物流</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.64&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
           <t>600604</t>
         </is>
       </c>
-      <c r="C205" s="10" t="inlineStr">
+      <c r="C208" s="10" t="inlineStr">
         <is>
           <t>市北高新</t>
         </is>
       </c>
-      <c r="D205" s="10" t="inlineStr">
+      <c r="D208" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.22&lt;5</t>
         </is>
@@ -5677,12 +5737,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600237</t>
+          <t>600246</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>铜峰电子</t>
+          <t>万通发展</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5691,7 +5751,7 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>-5.54</v>
+        <v>-6.24</v>
       </c>
       <c r="F2" s="10" t="n"/>
       <c r="G2" s="10" t="n">
@@ -5699,7 +5759,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>跌5.5%(简版)</t>
+          <t>跌6.2%(简版)</t>
         </is>
       </c>
     </row>
@@ -5709,12 +5769,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600207</t>
+          <t>600578</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>安彩高科</t>
+          <t>京能电力</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5723,7 +5783,7 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-5.61</v>
+        <v>-3.73</v>
       </c>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n">
@@ -5731,7 +5791,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>跌5.6%(简版)</t>
+          <t>跌3.7%(简版)</t>
         </is>
       </c>
     </row>
@@ -5741,12 +5801,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600549</t>
+          <t>600330</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>厦门钨业</t>
+          <t>天通股份</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5755,7 +5815,7 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-3.91</v>
+        <v>-3.62</v>
       </c>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n">
@@ -5763,7 +5823,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>跌3.9%(简版)</t>
+          <t>跌3.6%(简版)</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5899,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600237</t>
+          <t>600246</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>铜峰电子</t>
+          <t>万通发展</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5875,12 +5935,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600207</t>
+          <t>600578</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>安彩高科</t>
+          <t>京能电力</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5911,12 +5971,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600549</t>
+          <t>600330</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>厦门钨业</t>
+          <t>天通股份</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5990,7 +6050,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>600237 铜峰电子</t>
+          <t>600246 万通发展</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -6002,7 +6062,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>600207 安彩高科</t>
+          <t>600578 京能电力</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -6014,7 +6074,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>600549 厦门钨业</t>
+          <t>600330 天通股份</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>万通发展</t>
+          <t>通威股份</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600246</t>
+          <t>600438</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-6.24</v>
+        <v>-3.52</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16.07</v>
+        <v>13.7</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>10.44</v>
+        <v>4.37</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>16.07</v>
+        <v>13.7</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>15.43</v>
+        <v>13.15</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>16.87</v>
+        <v>14.38</v>
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600246.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600438.html</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>京能电力</t>
+          <t>三佳科技</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600578</t>
+          <t>600520</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-3.73</v>
+        <v>-6.53</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.8</v>
+        <v>29.4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7.49</v>
+        <v>26.89</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>6.04</v>
+        <v>10.01</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -773,17 +773,17 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>7.49</v>
+        <v>26.89</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>7.19</v>
+        <v>25.81</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>7.86</v>
+        <v>28.23</v>
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600578.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600520.html</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>中国国贸</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>600330</t>
+          <t>600007</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-3.62</v>
+        <v>-6.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>30.09</v>
+        <v>21.24</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28.25</v>
+        <v>19.78</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7.78</v>
+        <v>8.19</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -845,17 +845,17 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>28.25</v>
+        <v>19.78</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>27.12</v>
+        <v>18.99</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>29.66</v>
+        <v>20.77</v>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600330.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600007.html</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>207只</t>
+          <t>210只</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>8只</t>
+          <t>5只</t>
         </is>
       </c>
       <c r="C19" s="14" t="n"/>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D208"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>600247</t>
+          <t>600246</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>*ST成城</t>
+          <t>万通发展</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.65&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600247</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>陕建股份</t>
+          <t>*ST成城</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.02&lt;5</t>
+          <t>L1-规则3:股价0.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>600252</t>
+          <t>600248</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>中恒集团</t>
+          <t>陕建股份</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.16&lt;5</t>
+          <t>L1-规则3:股价3.02&lt;5</t>
         </is>
       </c>
     </row>
@@ -3149,17 +3149,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>600255</t>
+          <t>600252</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>鑫科材料</t>
+          <t>中恒集团</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.15&lt;5</t>
+          <t>L1-规则3:股价2.16&lt;5</t>
         </is>
       </c>
     </row>
@@ -3169,17 +3169,17 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>600260</t>
+          <t>600255</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>*ST凯乐</t>
+          <t>鑫科材料</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.47&lt;5</t>
+          <t>L1-规则3:股价4.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -3189,17 +3189,17 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>600261</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>*ST凯乐</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.19&lt;5</t>
+          <t>L1-规则3:股价0.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -3209,17 +3209,17 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>600265</t>
+          <t>600261</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>*ST景谷</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价3.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -3229,17 +3229,17 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>600266</t>
+          <t>600265</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>城建发展</t>
+          <t>*ST景谷</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.43&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3249,17 +3249,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>600269</t>
+          <t>600266</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>赣粤高速</t>
+          <t>城建发展</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.20&lt;5</t>
+          <t>L1-规则3:股价4.43&lt;5</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>600275</t>
+          <t>600269</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>退市昌鱼</t>
+          <t>赣粤高速</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -3289,17 +3289,17 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>600277</t>
+          <t>600275</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>ST亿利</t>
+          <t>退市昌鱼</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.38&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3309,17 +3309,17 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>600279</t>
+          <t>600277</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>重庆港</t>
+          <t>ST亿利</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.44&lt;5</t>
+          <t>L1-规则3:股价0.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>600280</t>
+          <t>600279</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>中央商场</t>
+          <t>重庆港</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.93&lt;5</t>
+          <t>L1-规则3:股价4.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -3349,17 +3349,17 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>600281</t>
+          <t>600280</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>华阳新材</t>
+          <t>中央商场</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.90&lt;5</t>
+          <t>L1-规则3:股价2.93&lt;5</t>
         </is>
       </c>
     </row>
@@ -3369,17 +3369,17 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>600282</t>
+          <t>600281</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>南钢股份</t>
+          <t>华阳新材</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.84&lt;5</t>
+          <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3389,17 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>600287</t>
+          <t>600282</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>苏豪时尚</t>
+          <t>南钢股份</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.90&lt;5</t>
+          <t>L1-规则3:股价4.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3409,17 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>600289</t>
+          <t>600287</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>ST信通</t>
+          <t>苏豪时尚</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3429,17 +3429,17 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>600290</t>
+          <t>600289</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>*ST华仪</t>
+          <t>ST信通</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>600291</t>
+          <t>600290</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>退市西水</t>
+          <t>*ST华仪</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.89&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -3469,17 +3469,17 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>600292</t>
+          <t>600291</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>电投水电</t>
+          <t>退市西水</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价0.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -3489,17 +3489,17 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>600293</t>
+          <t>600292</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>电投水电</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.41&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3509,17 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>600297</t>
+          <t>600293</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>广汇汽车</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.78&lt;5</t>
+          <t>L1-规则3:股价3.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3529,17 +3529,17 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>600297</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>广汇汽车</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.07&lt;5</t>
+          <t>L1-规则3:股价0.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -3549,17 +3549,17 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>600301</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>华锡有色</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.6%&gt;7%</t>
+          <t>L1-规则3:股价3.07&lt;5</t>
         </is>
       </c>
     </row>
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>600302</t>
+          <t>600301</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>ST标准</t>
+          <t>华锡有色</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则12:涨幅7.6%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3589,17 +3589,17 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>600303</t>
+          <t>600302</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>曙光股份</t>
+          <t>ST标准</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.04&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3609,17 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>600306</t>
+          <t>600303</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>退市商城</t>
+          <t>曙光股份</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.29&lt;5</t>
+          <t>L1-规则3:股价3.04&lt;5</t>
         </is>
       </c>
     </row>
@@ -3629,17 +3629,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>600307</t>
+          <t>600306</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>酒钢宏兴</t>
+          <t>退市商城</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.57&lt;5</t>
+          <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -3649,17 +3649,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>600308</t>
+          <t>600307</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>华泰股份</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.36&lt;5</t>
+          <t>L1-规则3:股价1.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3669,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>600310</t>
+          <t>600308</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>华泰股份</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.63&lt;5</t>
+          <t>L1-规则3:股价3.36&lt;5</t>
         </is>
       </c>
     </row>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>600311</t>
+          <t>600310</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>*ST荣华</t>
+          <t>广西能源</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.61&lt;5</t>
+          <t>L1-规则3:股价4.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3709,17 +3709,17 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>600317</t>
+          <t>600311</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>营口港</t>
+          <t>*ST荣华</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.60&lt;5</t>
+          <t>L1-规则3:股价0.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>600320</t>
+          <t>600317</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>振华重工</t>
+          <t>营口港</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价2.60&lt;5</t>
         </is>
       </c>
     </row>
@@ -3749,17 +3749,17 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>600321</t>
+          <t>600320</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>正源股份</t>
+          <t>振华重工</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.50&lt;5</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -3769,17 +3769,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>600322</t>
+          <t>600321</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>津投城开</t>
+          <t>正源股份</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.68&lt;5</t>
+          <t>L1-规则3:股价0.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>600325</t>
+          <t>600322</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>华发股份</t>
+          <t>津投城开</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.63&lt;5</t>
+          <t>L1-规则3:股价2.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>600327</t>
+          <t>600325</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>大东方</t>
+          <t>华发股份</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价2.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>600337</t>
+          <t>600327</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>ST美克</t>
+          <t>大东方</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3849,17 +3849,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>600339</t>
+          <t>600330</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>中油工程</t>
+          <t>天通股份</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.31&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>600340</t>
+          <t>600337</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>*ST华幸</t>
+          <t>ST美克</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.33&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3889,17 +3889,17 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>600346</t>
+          <t>600339</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>恒力石化</t>
+          <t>中油工程</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价3.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -3909,17 +3909,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>600355</t>
+          <t>600340</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>*ST精伦</t>
+          <t>*ST华幸</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.58&lt;5</t>
+          <t>L1-规则3:股价1.33&lt;5</t>
         </is>
       </c>
     </row>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>600361</t>
+          <t>600346</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>创新新材</t>
+          <t>恒力石化</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>600362</t>
+          <t>600355</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>江西铜业</t>
+          <t>*ST精伦</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价0.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -3969,17 +3969,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>600365</t>
+          <t>600361</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>ST通葡</t>
+          <t>创新新材</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.55&lt;5</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>600368</t>
+          <t>600362</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>五洲交通</t>
+          <t>江西铜业</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.78&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -4009,17 +4009,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>600369</t>
+          <t>600365</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>西南证券</t>
+          <t>ST通葡</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
+          <t>L1-规则3:股价2.55&lt;5</t>
         </is>
       </c>
     </row>
@@ -4029,17 +4029,17 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>600370</t>
+          <t>600368</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>*ST三房</t>
+          <t>五洲交通</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.46&lt;5</t>
+          <t>L1-规则3:股价3.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>600375</t>
+          <t>600369</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>汉马科技</t>
+          <t>西南证券</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.94&lt;5</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -4069,17 +4069,17 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>600376</t>
+          <t>600370</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>首开股份</t>
+          <t>*ST三房</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.40&lt;5</t>
+          <t>L1-规则3:股价1.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -4089,17 +4089,17 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>600378</t>
+          <t>600375</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>XD昊华科</t>
+          <t>汉马科技</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则3:股价3.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -4109,17 +4109,17 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>600381</t>
+          <t>600376</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>*ST春天</t>
+          <t>首开股份</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价3.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4129,17 +4129,17 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>600383</t>
+          <t>600378</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>金地集团</t>
+          <t>XD昊华科</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.51&lt;5</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -4149,17 +4149,17 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>600385</t>
+          <t>600381</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>退市金泰</t>
+          <t>*ST春天</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.20&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>600386</t>
+          <t>600383</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>北巴传媒</t>
+          <t>金地集团</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价2.51&lt;5</t>
         </is>
       </c>
     </row>
@@ -4189,17 +4189,17 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>600387</t>
+          <t>600385</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>退市海越</t>
+          <t>退市金泰</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.94&lt;5</t>
+          <t>L1-规则3:股价1.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -4209,17 +4209,17 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>600390</t>
+          <t>600386</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>五矿资本</t>
+          <t>北巴传媒</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.65&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -4229,17 +4229,17 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>600391</t>
+          <t>600387</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>航发科技</t>
+          <t>退市海越</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价0.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -4249,17 +4249,17 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>600393</t>
+          <t>600390</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>ST粤泰</t>
+          <t>五矿资本</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则3:股价4.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -4269,17 +4269,17 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>600391</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>抚顺特钢</t>
+          <t>航发科技</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.32&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4289,17 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>600400</t>
+          <t>600393</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>ST粤泰</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.61&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -4309,17 +4309,17 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>600401</t>
+          <t>600399</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>退市海润</t>
+          <t>抚顺特钢</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.15&lt;5</t>
+          <t>L1-规则3:股价4.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -4329,17 +4329,17 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>600403</t>
+          <t>600400</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>大有能源</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-9.9%</t>
+          <t>L1-规则3:股价2.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -4349,17 +4349,17 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>600405</t>
+          <t>600401</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>动力源</t>
+          <t>退市海润</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.26&lt;5</t>
+          <t>L1-规则3:股价0.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>600408</t>
+          <t>600403</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>大有能源</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.88&lt;5</t>
+          <t>L1-规则22:跌停-9.9%</t>
         </is>
       </c>
     </row>
@@ -4389,17 +4389,17 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>600421</t>
+          <t>600405</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>退市华嵘</t>
+          <t>动力源</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则3:股价4.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4409,17 +4409,17 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>600423</t>
+          <t>600408</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>*ST柳化</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.48&lt;5</t>
+          <t>L1-规则3:股价2.88&lt;5</t>
         </is>
       </c>
     </row>
@@ -4429,17 +4429,17 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>600425</t>
+          <t>600421</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>XD青松建</t>
+          <t>退市华嵘</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.54&lt;5</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4449,17 +4449,17 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>600429</t>
+          <t>600423</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>三元股份</t>
+          <t>*ST柳化</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价2.48&lt;5</t>
         </is>
       </c>
     </row>
@@ -4469,17 +4469,17 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>600432</t>
+          <t>600425</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>退市吉恩</t>
+          <t>XD青松建</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.38&lt;5</t>
+          <t>L1-规则3:股价3.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -4489,17 +4489,17 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>600433</t>
+          <t>600429</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>冠豪高新</t>
+          <t>三元股份</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.53&lt;5</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4509,17 +4509,17 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>600436</t>
+          <t>600432</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>片仔癀</t>
+          <t>退市吉恩</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价119.56&gt;100</t>
+          <t>L1-规则3:股价1.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>600439</t>
+          <t>600433</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>瑞贝卡</t>
+          <t>冠豪高新</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.27&lt;5</t>
+          <t>L1-规则3:股价3.53&lt;5</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>600448</t>
+          <t>600436</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>华纺股份</t>
+          <t>片仔癀</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则4:股价119.56&gt;100</t>
         </is>
       </c>
     </row>
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>600462</t>
+          <t>600439</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>退市九有</t>
+          <t>瑞贝卡</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.21&lt;5</t>
+          <t>L1-规则3:股价2.27&lt;5</t>
         </is>
       </c>
     </row>
@@ -4589,17 +4589,17 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>600466</t>
+          <t>600448</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>*ST蓝光</t>
+          <t>华纺股份</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.40&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -4609,17 +4609,17 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>600467</t>
+          <t>600462</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>好当家</t>
+          <t>退市九有</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则3:股价0.21&lt;5</t>
         </is>
       </c>
     </row>
@@ -4629,17 +4629,17 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>600476</t>
+          <t>600466</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>*ST湘邮</t>
+          <t>*ST蓝光</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价0.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4649,17 +4649,17 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>600477</t>
+          <t>600467</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>杭萧钢构</t>
+          <t>好当家</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.59&lt;5</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -4669,17 +4669,17 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>600485</t>
+          <t>600476</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>*ST信威</t>
+          <t>*ST湘邮</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.39&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>600477</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>杭萧钢构</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价2.59&lt;5</t>
         </is>
       </c>
     </row>
@@ -4709,17 +4709,17 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>600488</t>
+          <t>600485</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>*ST信威</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.76&lt;5</t>
+          <t>L1-规则3:股价1.39&lt;5</t>
         </is>
       </c>
     </row>
@@ -4729,17 +4729,17 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>600491</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>ST龙元</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.31&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4749,17 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>600495</t>
+          <t>600488</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>晋西车轴</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.80&lt;5</t>
+          <t>L1-规则3:股价4.76&lt;5</t>
         </is>
       </c>
     </row>
@@ -4769,17 +4769,17 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>600496</t>
+          <t>600491</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>精工钢构</t>
+          <t>ST龙元</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.84&lt;5</t>
+          <t>L1-规则3:股价1.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -4789,17 +4789,17 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>600497</t>
+          <t>600495</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>驰宏锌锗</t>
+          <t>晋西车轴</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停9.9%</t>
+          <t>L1-规则3:股价3.80&lt;5</t>
         </is>
       </c>
     </row>
@@ -4809,17 +4809,17 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>600500</t>
+          <t>600496</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>中化国际</t>
+          <t>精工钢构</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价3.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -4829,17 +4829,17 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>600502</t>
+          <t>600497</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>安徽建工</t>
+          <t>驰宏锌锗</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.68&lt;5</t>
+          <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
@@ -4849,17 +4849,17 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>600503</t>
+          <t>600500</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>中化国际</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.46&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>600507</t>
+          <t>600502</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>方大特钢</t>
+          <t>安徽建工</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.29&lt;5</t>
+          <t>L1-规则3:股价4.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -4889,17 +4889,17 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>600512</t>
+          <t>600503</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>腾达建设</t>
+          <t>华丽家族</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.08&lt;5</t>
+          <t>L1-规则3:股价2.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -4909,17 +4909,17 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>600515</t>
+          <t>600507</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>海南机场</t>
+          <t>方大特钢</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.98&lt;5</t>
+          <t>L1-规则3:股价4.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>600517</t>
+          <t>600512</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>国网英大</t>
+          <t>腾达建设</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则3:股价2.08&lt;5</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4949,17 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>600518</t>
+          <t>600515</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>康美药业</t>
+          <t>海南机场</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.40&lt;5</t>
+          <t>L1-规则3:股价2.98&lt;5</t>
         </is>
       </c>
     </row>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600517</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>国网英大</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价1291.91&gt;100</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -4989,17 +4989,17 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>600525</t>
+          <t>600518</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>康美药业</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.99&lt;5</t>
+          <t>L1-规则3:股价1.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -5009,17 +5009,17 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>600526</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>菲达环保</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.49&lt;5</t>
+          <t>L1-规则4:股价1291.91&gt;100</t>
         </is>
       </c>
     </row>
@@ -5029,17 +5029,17 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>600527</t>
+          <t>600525</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>江南高纤</t>
+          <t>ST长园</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.32&lt;5</t>
+          <t>L1-规则3:股价4.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>600531</t>
+          <t>600526</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>豫光金铅</t>
+          <t>菲达环保</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.49&lt;5</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5069,17 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>600532</t>
+          <t>600527</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>退市未来</t>
+          <t>江南高纤</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.72&lt;5</t>
+          <t>L1-规则3:股价2.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -5089,17 +5089,17 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>600533</t>
+          <t>600531</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>栖霞建设</t>
+          <t>豫光金铅</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5109,17 +5109,17 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>600536</t>
+          <t>600532</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>中国软件</t>
+          <t>退市未来</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则3:股价0.72&lt;5</t>
         </is>
       </c>
     </row>
@@ -5129,17 +5129,17 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>600537</t>
+          <t>600533</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>*ST亿晶</t>
+          <t>栖霞建设</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.58&lt;5</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5149,17 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>600539</t>
+          <t>600536</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>狮头股份</t>
+          <t>中国软件</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -5169,17 +5169,17 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>600540</t>
+          <t>600537</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>新赛股份</t>
+          <t>*ST亿晶</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.46&lt;5</t>
+          <t>L1-规则3:股价2.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5189,17 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>600543</t>
+          <t>600539</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>*ST莫高</t>
+          <t>狮头股份</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.22&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5209,17 +5209,17 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>600549</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>厦门钨业</t>
+          <t>新赛股份</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价4.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>600555</t>
+          <t>600543</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>退市海创</t>
+          <t>*ST莫高</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则3:股价4.22&lt;5</t>
         </is>
       </c>
     </row>
@@ -5249,17 +5249,17 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>600556</t>
+          <t>600549</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>天下秀</t>
+          <t>厦门钨业</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -5269,17 +5269,17 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>600563</t>
+          <t>600555</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>XD法拉电</t>
+          <t>退市海创</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价143.00&gt;100</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -5289,17 +5289,17 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>600565</t>
+          <t>600556</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>ST迪马</t>
+          <t>天下秀</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.85&lt;5</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -5309,17 +5309,17 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>600567</t>
+          <t>600563</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>山鹰国际</t>
+          <t>XD法拉电</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.44&lt;5</t>
+          <t>L1-规则4:股价143.00&gt;100</t>
         </is>
       </c>
     </row>
@@ -5329,17 +5329,17 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>600568</t>
+          <t>600565</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>ST中珠</t>
+          <t>ST迪马</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.54&lt;5</t>
+          <t>L1-规则3:股价0.85&lt;5</t>
         </is>
       </c>
     </row>
@@ -5349,17 +5349,17 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>600569</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>安阳钢铁</t>
+          <t>山鹰国际</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.87&lt;5</t>
+          <t>L1-规则3:股价1.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>600572</t>
+          <t>600568</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>康恩贝</t>
+          <t>ST中珠</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则3:股价2.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>600575</t>
+          <t>600569</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>淮河能源</t>
+          <t>安阳钢铁</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
+          <t>L1-规则3:股价1.87&lt;5</t>
         </is>
       </c>
     </row>
@@ -5409,17 +5409,17 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>600576</t>
+          <t>600572</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>祥源文旅</t>
+          <t>康恩贝</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -5429,17 +5429,17 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>600581</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>*ST八钢</t>
+          <t>淮河能源</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.57&lt;5</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -5449,17 +5449,17 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>600586</t>
+          <t>600576</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>金晶科技</t>
+          <t>祥源文旅</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.57&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5469,12 +5469,12 @@
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>600592</t>
+          <t>600578</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>龙溪股份</t>
+          <t>京能电力</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
@@ -5489,17 +5489,17 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>600594</t>
+          <t>600581</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>益佰制药</t>
+          <t>*ST八钢</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.29&lt;5</t>
+          <t>L1-规则3:股价2.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5509,17 +5509,17 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>600599</t>
+          <t>600586</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>退市熊猫</t>
+          <t>金晶科技</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5529,17 +5529,17 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>600601</t>
+          <t>600592</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>方正科技</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则13:7日内已推荐</t>
         </is>
       </c>
     </row>
@@ -5549,17 +5549,17 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>600603</t>
+          <t>600594</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>广汇物流</t>
+          <t>益佰制药</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.64&lt;5</t>
+          <t>L1-规则3:股价3.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -5569,15 +5569,75 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
+          <t>600599</t>
+        </is>
+      </c>
+      <c r="C208" s="10" t="inlineStr">
+        <is>
+          <t>退市熊猫</t>
+        </is>
+      </c>
+      <c r="D208" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价0.41&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="10" t="inlineStr">
+        <is>
+          <t>600601</t>
+        </is>
+      </c>
+      <c r="C209" s="10" t="inlineStr">
+        <is>
+          <t>方正科技</t>
+        </is>
+      </c>
+      <c r="D209" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则11:涨停10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>600603</t>
+        </is>
+      </c>
+      <c r="C210" s="10" t="inlineStr">
+        <is>
+          <t>广汇物流</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="inlineStr">
+        <is>
+          <t>L1-规则3:股价4.64&lt;5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="10" t="inlineStr">
+        <is>
           <t>600604</t>
         </is>
       </c>
-      <c r="C208" s="10" t="inlineStr">
+      <c r="C211" s="10" t="inlineStr">
         <is>
           <t>市北高新</t>
         </is>
       </c>
-      <c r="D208" s="10" t="inlineStr">
+      <c r="D211" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.22&lt;5</t>
         </is>
@@ -5737,12 +5797,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600246</t>
+          <t>600438</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>万通发展</t>
+          <t>通威股份</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5751,7 +5811,7 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>-6.24</v>
+        <v>-3.52</v>
       </c>
       <c r="F2" s="10" t="n"/>
       <c r="G2" s="10" t="n">
@@ -5759,7 +5819,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>跌6.2%(简版)</t>
+          <t>跌3.5%(简版)</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5829,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600578</t>
+          <t>600520</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>京能电力</t>
+          <t>三佳科技</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5783,7 +5843,7 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-3.73</v>
+        <v>-6.53</v>
       </c>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n">
@@ -5791,7 +5851,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>跌3.7%(简版)</t>
+          <t>跌6.5%(简版)</t>
         </is>
       </c>
     </row>
@@ -5801,12 +5861,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600330</t>
+          <t>600007</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>中国国贸</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5815,7 +5875,7 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-3.62</v>
+        <v>-6.92</v>
       </c>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n">
@@ -5823,7 +5883,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>跌3.6%(简版)</t>
+          <t>跌6.9%(简版)</t>
         </is>
       </c>
     </row>
@@ -5899,12 +5959,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600246</t>
+          <t>600438</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>万通发展</t>
+          <t>通威股份</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5935,12 +5995,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600578</t>
+          <t>600520</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>京能电力</t>
+          <t>三佳科技</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5971,12 +6031,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600330</t>
+          <t>600007</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>中国国贸</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -6050,7 +6110,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>600246 万通发展</t>
+          <t>600438 通威股份</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -6062,7 +6122,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>600578 京能电力</t>
+          <t>600520 三佳科技</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -6074,7 +6134,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>600330 天通股份</t>
+          <t>600007 中国国贸</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>通威股份</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600438</t>
+          <t>600592</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-3.52</v>
+        <v>-5.18</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>14.2</v>
+        <v>16.64</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13.7</v>
+        <v>15.56</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.37</v>
+        <v>7.86</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>13.7</v>
+        <v>15.56</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>13.15</v>
+        <v>14.94</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>14.38</v>
+        <v>16.34</v>
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600438.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600592.html</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>三佳科技</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600520</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-6.53</v>
+        <v>-5.27</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>29.4</v>
+        <v>105.08</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.89</v>
+        <v>97</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>10.01</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -773,17 +773,17 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>26.89</v>
+        <v>97</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>25.81</v>
+        <v>93.12</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>28.23</v>
+        <v>101.85</v>
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600520.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600487.html</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>中国国贸</t>
+          <t>科新发展</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>600007</t>
+          <t>600234</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-6.92</v>
+        <v>-4.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>21.24</v>
+        <v>25.57</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19.78</v>
+        <v>24.39</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>8.19</v>
+        <v>6.81</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -845,17 +845,17 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>19.78</v>
+        <v>24.39</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>18.99</v>
+        <v>23.41</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>20.77</v>
+        <v>25.61</v>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600007.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600234.html</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>210只</t>
+          <t>200只</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>5只</t>
+          <t>15只</t>
         </is>
       </c>
       <c r="C19" s="14" t="n"/>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>600063</t>
+          <t>600067</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>皖维高新</t>
+          <t>冠城新材</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价3.48&lt;5</t>
         </is>
       </c>
     </row>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>600067</t>
+          <t>600069</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>冠城新材</t>
+          <t>退市银鸽</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.48&lt;5</t>
+          <t>L1-规则3:股价0.28&lt;5</t>
         </is>
       </c>
     </row>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>600069</t>
+          <t>600070</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>退市银鸽</t>
+          <t>*ST富润</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.28&lt;5</t>
+          <t>L1-规则3:股价0.42&lt;5</t>
         </is>
       </c>
     </row>
@@ -1769,17 +1769,17 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>600070</t>
+          <t>600074</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>*ST富润</t>
+          <t>退市保千</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.42&lt;5</t>
+          <t>L1-规则3:股价0.17&lt;5</t>
         </is>
       </c>
     </row>
@@ -1789,17 +1789,17 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>600074</t>
+          <t>600075</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>退市保千</t>
+          <t>新疆天业</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.17&lt;5</t>
+          <t>L1-规则3:股价4.75&lt;5</t>
         </is>
       </c>
     </row>
@@ -1809,17 +1809,17 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>600075</t>
+          <t>600076</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>新疆天业</t>
+          <t>康欣新材</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.75&lt;5</t>
+          <t>L1-规则3:股价3.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -1829,17 +1829,17 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>600076</t>
+          <t>600077</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>康欣新材</t>
+          <t>*ST宋都</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.47&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -1849,17 +1849,17 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>600077</t>
+          <t>600079</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>*ST宋都</t>
+          <t>ST人福</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>600079</t>
+          <t>600080</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>ST人福</t>
+          <t>ST金花</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价4.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -1889,17 +1889,17 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>600080</t>
+          <t>600082</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>ST金花</t>
+          <t>ST海泰</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.78&lt;5</t>
+          <t>L1-规则3:股价3.05&lt;5</t>
         </is>
       </c>
     </row>
@@ -1909,17 +1909,17 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>600082</t>
+          <t>600083</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>ST海泰</t>
+          <t>*ST博信</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.05&lt;5</t>
+          <t>L1-规则3:股价0.92&lt;5</t>
         </is>
       </c>
     </row>
@@ -1929,17 +1929,17 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>600083</t>
+          <t>600084</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>*ST博信</t>
+          <t>*ST尼雅</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.92&lt;5</t>
+          <t>L1-规则3:股价4.27&lt;5</t>
         </is>
       </c>
     </row>
@@ -1949,17 +1949,17 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>600084</t>
+          <t>600086</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>*ST尼雅</t>
+          <t>退市金钰</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.27&lt;5</t>
+          <t>L1-规则3:股价0.16&lt;5</t>
         </is>
       </c>
     </row>
@@ -1969,17 +1969,17 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>600086</t>
+          <t>600090</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>退市金钰</t>
+          <t>退市济堂</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.16&lt;5</t>
+          <t>L1-规则3:股价0.27&lt;5</t>
         </is>
       </c>
     </row>
@@ -1989,17 +1989,17 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>600090</t>
+          <t>600091</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>退市济堂</t>
+          <t>退市明科</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.27&lt;5</t>
+          <t>L1-规则3:股价0.76&lt;5</t>
         </is>
       </c>
     </row>
@@ -2009,17 +2009,17 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>600091</t>
+          <t>600093</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>退市明科</t>
+          <t>退市易见</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.76&lt;5</t>
+          <t>L1-规则3:股价0.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2029,17 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>600093</t>
+          <t>600094</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>退市易见</t>
+          <t>大名城</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.50&lt;5</t>
+          <t>L1-规则3:股价3.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -2049,17 +2049,17 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>600094</t>
+          <t>600103</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>大名城</t>
+          <t>青山纸业</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.90&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -2069,17 +2069,17 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>600103</t>
+          <t>600107</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>青山纸业</t>
+          <t>*ST尔雅</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -2089,17 +2089,17 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>600107</t>
+          <t>600108</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>*ST尔雅</t>
+          <t>亚盛集团</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价3.59&lt;5</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2109,17 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>600108</t>
+          <t>600112</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>*ST天成</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.59&lt;5</t>
+          <t>L1-规则3:股价0.73&lt;5</t>
         </is>
       </c>
     </row>
@@ -2129,17 +2129,17 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>600112</t>
+          <t>600115</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>*ST天成</t>
+          <t>中国东航</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.73&lt;5</t>
+          <t>L1-规则3:股价3.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -2149,17 +2149,17 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>600115</t>
+          <t>600117</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>中国东航</t>
+          <t>西宁特钢</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.90&lt;5</t>
+          <t>L1-规则3:股价2.27&lt;5</t>
         </is>
       </c>
     </row>
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>600117</t>
+          <t>600119</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>西宁特钢</t>
+          <t>*ST长投</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.27&lt;5</t>
+          <t>L1-规则3:股价4.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -2189,17 +2189,17 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>600119</t>
+          <t>600120</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>*ST长投</t>
+          <t>浙江东方</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.84&lt;5</t>
+          <t>L1-规则3:股价4.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>600120</t>
+          <t>600121</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>浙江东方</t>
+          <t>郑州煤电</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.47&lt;5</t>
+          <t>L1-规则3:股价4.51&lt;5</t>
         </is>
       </c>
     </row>
@@ -2229,17 +2229,17 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>600121</t>
+          <t>600122</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>郑州煤电</t>
+          <t>*ST宏图</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.51&lt;5</t>
+          <t>L1-规则3:股价0.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -2249,17 +2249,17 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>600122</t>
+          <t>600130</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>*ST宏图</t>
+          <t>波导股份</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.38&lt;5</t>
+          <t>L1-规则3:股价4.53&lt;5</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>600130</t>
+          <t>600136</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>波导股份</t>
+          <t>ST明诚</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.53&lt;5</t>
+          <t>L1-规则3:股价1.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -2289,17 +2289,17 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>600136</t>
+          <t>600139</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>ST明诚</t>
+          <t>*ST西源</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.47&lt;5</t>
+          <t>L1-规则3:股价0.74&lt;5</t>
         </is>
       </c>
     </row>
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>600139</t>
+          <t>600145</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>*ST西源</t>
+          <t>退市新亿</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.74&lt;5</t>
+          <t>L1-规则3:股价0.34&lt;5</t>
         </is>
       </c>
     </row>
@@ -2329,17 +2329,17 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>600145</t>
+          <t>600146</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>退市新亿</t>
+          <t>退市环球</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.34&lt;5</t>
+          <t>L1-规则3:股价0.22&lt;5</t>
         </is>
       </c>
     </row>
@@ -2349,17 +2349,17 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>600146</t>
+          <t>600157</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>退市环球</t>
+          <t>永泰能源</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.22&lt;5</t>
+          <t>L1-规则3:股价1.70&lt;5</t>
         </is>
       </c>
     </row>
@@ -2369,17 +2369,17 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>600157</t>
+          <t>600159</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>永泰能源</t>
+          <t>大龙地产</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.70&lt;5</t>
+          <t>L1-规则3:股价2.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -2389,17 +2389,17 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>600159</t>
+          <t>600162</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>大龙地产</t>
+          <t>香江控股</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.63&lt;5</t>
+          <t>L1-规则3:股价3.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -2409,17 +2409,17 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>600162</t>
+          <t>600163</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>香江控股</t>
+          <t>中闽能源</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.47&lt;5</t>
+          <t>L1-规则12:涨幅9.7%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -2429,17 +2429,17 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>600163</t>
+          <t>600165</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>中闽能源</t>
+          <t>ST宁科</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅9.7%&gt;7%</t>
+          <t>L1-规则3:股价2.83&lt;5</t>
         </is>
       </c>
     </row>
@@ -2449,17 +2449,17 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>600165</t>
+          <t>600166</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>ST宁科</t>
+          <t>福田汽车</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.83&lt;5</t>
+          <t>L1-规则3:股价3.10&lt;5</t>
         </is>
       </c>
     </row>
@@ -2469,17 +2469,17 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>600166</t>
+          <t>600168</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>福田汽车</t>
+          <t>武汉控股</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.10&lt;5</t>
+          <t>L1-规则3:股价4.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -2489,17 +2489,17 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>600168</t>
+          <t>600169</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>武汉控股</t>
+          <t>ST太重</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.46&lt;5</t>
+          <t>L1-规则3:股价2.24&lt;5</t>
         </is>
       </c>
     </row>
@@ -2509,17 +2509,17 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>600169</t>
+          <t>600170</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>ST太重</t>
+          <t>上海建工</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.24&lt;5</t>
+          <t>L1-规则3:股价2.42&lt;5</t>
         </is>
       </c>
     </row>
@@ -2529,17 +2529,17 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>600170</t>
+          <t>600175</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>上海建工</t>
+          <t>退市美都</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.42&lt;5</t>
+          <t>L1-规则3:股价0.21&lt;5</t>
         </is>
       </c>
     </row>
@@ -2549,17 +2549,17 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>600175</t>
+          <t>600179</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>退市美都</t>
+          <t>安通控股</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.21&lt;5</t>
+          <t>L1-规则3:股价4.56&lt;5</t>
         </is>
       </c>
     </row>
@@ -2569,17 +2569,17 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>600179</t>
+          <t>600180</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>安通控股</t>
+          <t>*ST瑞茂</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.56&lt;5</t>
+          <t>L1-规则3:股价1.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -2589,17 +2589,17 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>600180</t>
+          <t>600183</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>*ST瑞茂</t>
+          <t>生益科技</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.32&lt;5</t>
+          <t>L1-规则4:股价151.28&gt;100</t>
         </is>
       </c>
     </row>
@@ -2609,17 +2609,17 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>600183</t>
+          <t>600187</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>生益科技</t>
+          <t>*ST国中</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价151.28&gt;100</t>
+          <t>L1-规则3:股价1.52&lt;5</t>
         </is>
       </c>
     </row>
@@ -2629,17 +2629,17 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>600187</t>
+          <t>600190</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>*ST国中</t>
+          <t>退市锦港</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.52&lt;5</t>
+          <t>L1-规则3:股价0.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>600190</t>
+          <t>600193</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>退市锦港</t>
+          <t>退市创兴</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.63&lt;5</t>
+          <t>L1-规则3:股价0.16&lt;5</t>
         </is>
       </c>
     </row>
@@ -2669,17 +2669,17 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>600193</t>
+          <t>600200</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>退市创兴</t>
+          <t>退市苏吴</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.16&lt;5</t>
+          <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -2689,17 +2689,17 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>600200</t>
+          <t>600208</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>退市苏吴</t>
+          <t>衢州发展</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.29&lt;5</t>
+          <t>L1-规则3:股价2.97&lt;5</t>
         </is>
       </c>
     </row>
@@ -2709,17 +2709,17 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>600207</t>
+          <t>600209</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>安彩高科</t>
+          <t>退市罗顿</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价1.18&lt;5</t>
         </is>
       </c>
     </row>
@@ -2729,17 +2729,17 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>600208</t>
+          <t>600213</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>衢州发展</t>
+          <t>*ST亚星</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.97&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>600209</t>
+          <t>600217</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>退市罗顿</t>
+          <t>中再资环</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.18&lt;5</t>
+          <t>L1-规则3:股价3.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -2769,17 +2769,17 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>600213</t>
+          <t>600219</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>*ST亚星</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价4.73&lt;5</t>
         </is>
       </c>
     </row>
@@ -2789,17 +2789,17 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>600217</t>
+          <t>600220</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>中再资环</t>
+          <t>ST阳光</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.15&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -2809,17 +2809,17 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>600219</t>
+          <t>600221</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>海航控股</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.73&lt;5</t>
+          <t>L1-规则3:股价1.53&lt;5</t>
         </is>
       </c>
     </row>
@@ -2829,17 +2829,17 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>600220</t>
+          <t>600225</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>ST阳光</t>
+          <t>退市卓朗</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -2849,17 +2849,17 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>600221</t>
+          <t>600227</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>海航控股</t>
+          <t>赤天化</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.53&lt;5</t>
+          <t>L1-规则3:股价2.87&lt;5</t>
         </is>
       </c>
     </row>
@@ -2869,17 +2869,17 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>600225</t>
+          <t>600229</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>退市卓朗</t>
+          <t>城市传媒</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.29&lt;5</t>
+          <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>600227</t>
+          <t>600231</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>赤天化</t>
+          <t>凌钢股份</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.87&lt;5</t>
+          <t>L1-规则3:股价1.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -2909,17 +2909,17 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>600229</t>
+          <t>600238</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>城市传媒</t>
+          <t>*ST椰岛</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停9.9%</t>
+          <t>L1-规则3:股价4.91&lt;5</t>
         </is>
       </c>
     </row>
@@ -2929,17 +2929,17 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>600231</t>
+          <t>600239</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>凌钢股份</t>
+          <t>ST云城</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.89&lt;5</t>
+          <t>L1-规则3:股价1.42&lt;5</t>
         </is>
       </c>
     </row>
@@ -2949,17 +2949,17 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>600234</t>
+          <t>600240</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>科新发展</t>
+          <t>退市华业</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -2969,17 +2969,17 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>600237</t>
+          <t>600242</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>铜峰电子</t>
+          <t>退市中昌</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价0.25&lt;5</t>
         </is>
       </c>
     </row>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>600238</t>
+          <t>600243</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>*ST椰岛</t>
+          <t>*ST海华</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.91&lt;5</t>
+          <t>L1-规则3:股价4.02&lt;5</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>600239</t>
+          <t>600247</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>ST云城</t>
+          <t>*ST成城</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.42&lt;5</t>
+          <t>L1-规则3:股价0.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -3029,17 +3029,17 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>600240</t>
+          <t>600248</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>退市华业</t>
+          <t>陕建股份</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价3.02&lt;5</t>
         </is>
       </c>
     </row>
@@ -3049,17 +3049,17 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>600242</t>
+          <t>600252</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>退市中昌</t>
+          <t>中恒集团</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.25&lt;5</t>
+          <t>L1-规则3:股价2.16&lt;5</t>
         </is>
       </c>
     </row>
@@ -3069,17 +3069,17 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>600243</t>
+          <t>600255</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>*ST海华</t>
+          <t>鑫科材料</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.02&lt;5</t>
+          <t>L1-规则3:股价4.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>600246</t>
+          <t>600260</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>万通发展</t>
+          <t>*ST凯乐</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价0.47&lt;5</t>
         </is>
       </c>
     </row>
@@ -3109,17 +3109,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>600247</t>
+          <t>600261</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>*ST成城</t>
+          <t>阳光照明</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.65&lt;5</t>
+          <t>L1-规则3:股价3.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600265</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>陕建股份</t>
+          <t>*ST景谷</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.02&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3149,17 +3149,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>600252</t>
+          <t>600266</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>中恒集团</t>
+          <t>城建发展</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.16&lt;5</t>
+          <t>L1-规则3:股价4.43&lt;5</t>
         </is>
       </c>
     </row>
@@ -3169,17 +3169,17 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>600255</t>
+          <t>600269</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>鑫科材料</t>
+          <t>赣粤高速</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.15&lt;5</t>
+          <t>L1-规则3:股价4.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -3189,17 +3189,17 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>600260</t>
+          <t>600275</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>*ST凯乐</t>
+          <t>退市昌鱼</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.47&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3209,17 +3209,17 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>600261</t>
+          <t>600277</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>ST亿利</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.19&lt;5</t>
+          <t>L1-规则3:股价0.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -3229,17 +3229,17 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>600265</t>
+          <t>600279</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>*ST景谷</t>
+          <t>重庆港</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价4.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -3249,17 +3249,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>600266</t>
+          <t>600280</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>城建发展</t>
+          <t>中央商场</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.43&lt;5</t>
+          <t>L1-规则3:股价2.93&lt;5</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>600269</t>
+          <t>600281</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>赣粤高速</t>
+          <t>华阳新材</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.20&lt;5</t>
+          <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3289,17 +3289,17 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>600275</t>
+          <t>600282</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>退市昌鱼</t>
+          <t>南钢股份</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
+          <t>L1-规则3:股价4.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -3309,17 +3309,17 @@
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>600277</t>
+          <t>600287</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>ST亿利</t>
+          <t>苏豪时尚</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.38&lt;5</t>
+          <t>L1-规则3:股价4.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>600279</t>
+          <t>600289</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>重庆港</t>
+          <t>ST信通</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.44&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3349,17 +3349,17 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>600280</t>
+          <t>600290</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>中央商场</t>
+          <t>*ST华仪</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.93&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -3369,17 +3369,17 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>600281</t>
+          <t>600291</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>华阳新材</t>
+          <t>退市西水</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.90&lt;5</t>
+          <t>L1-规则3:股价0.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3389,17 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>600282</t>
+          <t>600292</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>南钢股份</t>
+          <t>电投水电</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.84&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -3409,17 +3409,17 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>600287</t>
+          <t>600293</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>苏豪时尚</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.90&lt;5</t>
+          <t>L1-规则3:股价3.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -3429,17 +3429,17 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>600289</t>
+          <t>600297</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>ST信通</t>
+          <t>广汇汽车</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价0.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>600290</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>*ST华仪</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则3:股价3.07&lt;5</t>
         </is>
       </c>
     </row>
@@ -3469,17 +3469,17 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>600291</t>
+          <t>600301</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>退市西水</t>
+          <t>华锡有色</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.89&lt;5</t>
+          <t>L1-规则12:涨幅7.6%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3489,17 +3489,17 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>600292</t>
+          <t>600302</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>电投水电</t>
+          <t>ST标准</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3509,17 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>600293</t>
+          <t>600303</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>三峡新材</t>
+          <t>曙光股份</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.41&lt;5</t>
+          <t>L1-规则3:股价3.04&lt;5</t>
         </is>
       </c>
     </row>
@@ -3529,17 +3529,17 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>600297</t>
+          <t>600306</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>广汇汽车</t>
+          <t>退市商城</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.78&lt;5</t>
+          <t>L1-规则3:股价0.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -3549,17 +3549,17 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>600307</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.07&lt;5</t>
+          <t>L1-规则3:股价1.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>600301</t>
+          <t>600308</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>华锡有色</t>
+          <t>华泰股份</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.6%&gt;7%</t>
+          <t>L1-规则3:股价3.36&lt;5</t>
         </is>
       </c>
     </row>
@@ -3589,17 +3589,17 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>600302</t>
+          <t>600310</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>ST标准</t>
+          <t>广西能源</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价4.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3609,17 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>600303</t>
+          <t>600311</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>曙光股份</t>
+          <t>*ST荣华</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.04&lt;5</t>
+          <t>L1-规则3:股价0.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -3629,17 +3629,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>600306</t>
+          <t>600317</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>退市商城</t>
+          <t>营口港</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.29&lt;5</t>
+          <t>L1-规则3:股价2.60&lt;5</t>
         </is>
       </c>
     </row>
@@ -3649,17 +3649,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>600307</t>
+          <t>600320</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>酒钢宏兴</t>
+          <t>振华重工</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.57&lt;5</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3669,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>600308</t>
+          <t>600321</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>华泰股份</t>
+          <t>正源股份</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.36&lt;5</t>
+          <t>L1-规则3:股价0.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>600310</t>
+          <t>600322</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>津投城开</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.63&lt;5</t>
+          <t>L1-规则3:股价2.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -3709,17 +3709,17 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>600311</t>
+          <t>600325</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>*ST荣华</t>
+          <t>华发股份</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.61&lt;5</t>
+          <t>L1-规则3:股价2.63&lt;5</t>
         </is>
       </c>
     </row>
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>600317</t>
+          <t>600327</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>营口港</t>
+          <t>大东方</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.60&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -3749,17 +3749,17 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>600320</t>
+          <t>600337</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>振华重工</t>
+          <t>ST美克</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -3769,17 +3769,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>600321</t>
+          <t>600339</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>正源股份</t>
+          <t>中油工程</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.50&lt;5</t>
+          <t>L1-规则3:股价3.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -3789,17 +3789,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>600322</t>
+          <t>600340</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>津投城开</t>
+          <t>*ST华幸</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.68&lt;5</t>
+          <t>L1-规则3:股价1.33&lt;5</t>
         </is>
       </c>
     </row>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>600325</t>
+          <t>600346</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>华发股份</t>
+          <t>恒力石化</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.63&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>600327</t>
+          <t>600355</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>大东方</t>
+          <t>*ST精伦</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价0.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -3849,17 +3849,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>600330</t>
+          <t>600361</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>天通股份</t>
+          <t>创新新材</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>600337</t>
+          <t>600362</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>ST美克</t>
+          <t>江西铜业</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则12:涨幅7.2%&gt;7%</t>
         </is>
       </c>
     </row>
@@ -3889,17 +3889,17 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>600339</t>
+          <t>600365</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>中油工程</t>
+          <t>ST通葡</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.31&lt;5</t>
+          <t>L1-规则3:股价2.55&lt;5</t>
         </is>
       </c>
     </row>
@@ -3909,17 +3909,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>600340</t>
+          <t>600368</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>*ST华幸</t>
+          <t>五洲交通</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.33&lt;5</t>
+          <t>L1-规则3:股价3.78&lt;5</t>
         </is>
       </c>
     </row>
@@ -3929,17 +3929,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>600346</t>
+          <t>600369</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>恒力石化</t>
+          <t>西南证券</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>600355</t>
+          <t>600370</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>*ST精伦</t>
+          <t>*ST三房</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.58&lt;5</t>
+          <t>L1-规则3:股价1.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -3969,17 +3969,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>600361</t>
+          <t>600375</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>创新新材</t>
+          <t>汉马科技</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则3:股价3.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>600362</t>
+          <t>600376</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>江西铜业</t>
+          <t>首开股份</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>L1-规则12:涨幅7.2%&gt;7%</t>
+          <t>L1-规则3:股价3.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4009,17 +4009,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>600365</t>
+          <t>600378</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>ST通葡</t>
+          <t>XD昊华科</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.55&lt;5</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -4029,17 +4029,17 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>600368</t>
+          <t>600381</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>五洲交通</t>
+          <t>*ST春天</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.78&lt;5</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>600369</t>
+          <t>600383</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>西南证券</t>
+          <t>金地集团</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
+          <t>L1-规则3:股价2.51&lt;5</t>
         </is>
       </c>
     </row>
@@ -4069,17 +4069,17 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>600370</t>
+          <t>600385</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>*ST三房</t>
+          <t>退市金泰</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.46&lt;5</t>
+          <t>L1-规则3:股价1.20&lt;5</t>
         </is>
       </c>
     </row>
@@ -4089,17 +4089,17 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>600375</t>
+          <t>600386</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>汉马科技</t>
+          <t>北巴传媒</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.94&lt;5</t>
+          <t>L1-规则3:股价3.50&lt;5</t>
         </is>
       </c>
     </row>
@@ -4109,17 +4109,17 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>600376</t>
+          <t>600387</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>首开股份</t>
+          <t>退市海越</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.40&lt;5</t>
+          <t>L1-规则3:股价0.94&lt;5</t>
         </is>
       </c>
     </row>
@@ -4129,17 +4129,17 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>600378</t>
+          <t>600390</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>XD昊华科</t>
+          <t>五矿资本</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则3:股价4.65&lt;5</t>
         </is>
       </c>
     </row>
@@ -4149,17 +4149,17 @@
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>600381</t>
+          <t>600391</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>*ST春天</t>
+          <t>航发科技</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4169,17 +4169,17 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>600383</t>
+          <t>600393</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>金地集团</t>
+          <t>ST粤泰</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.51&lt;5</t>
+          <t>L1-规则3:股价0.37&lt;5</t>
         </is>
       </c>
     </row>
@@ -4189,17 +4189,17 @@
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>600385</t>
+          <t>600399</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>退市金泰</t>
+          <t>抚顺特钢</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.20&lt;5</t>
+          <t>L1-规则3:股价4.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -4209,17 +4209,17 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>600386</t>
+          <t>600400</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>北巴传媒</t>
+          <t>红豆股份</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.50&lt;5</t>
+          <t>L1-规则3:股价2.61&lt;5</t>
         </is>
       </c>
     </row>
@@ -4229,17 +4229,17 @@
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>600387</t>
+          <t>600401</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>退市海越</t>
+          <t>退市海润</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.94&lt;5</t>
+          <t>L1-规则3:股价0.15&lt;5</t>
         </is>
       </c>
     </row>
@@ -4249,17 +4249,17 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>600390</t>
+          <t>600403</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>五矿资本</t>
+          <t>大有能源</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.65&lt;5</t>
+          <t>L1-规则22:跌停-9.9%</t>
         </is>
       </c>
     </row>
@@ -4269,17 +4269,17 @@
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>600391</t>
+          <t>600405</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>航发科技</t>
+          <t>动力源</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4289,17 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>600393</t>
+          <t>600408</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>ST粤泰</t>
+          <t>安泰集团</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.37&lt;5</t>
+          <t>L1-规则3:股价2.88&lt;5</t>
         </is>
       </c>
     </row>
@@ -4309,17 +4309,17 @@
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>600421</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>抚顺特钢</t>
+          <t>退市华嵘</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.32&lt;5</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -4329,17 +4329,17 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>600400</t>
+          <t>600423</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>红豆股份</t>
+          <t>*ST柳化</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.61&lt;5</t>
+          <t>L1-规则3:股价2.48&lt;5</t>
         </is>
       </c>
     </row>
@@ -4349,17 +4349,17 @@
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>600401</t>
+          <t>600425</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>退市海润</t>
+          <t>XD青松建</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.15&lt;5</t>
+          <t>L1-规则3:股价3.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>600403</t>
+          <t>600429</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>大有能源</t>
+          <t>三元股份</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-9.9%</t>
+          <t>L1-规则3:股价4.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4389,17 +4389,17 @@
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>600405</t>
+          <t>600432</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>动力源</t>
+          <t>退市吉恩</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.26&lt;5</t>
+          <t>L1-规则3:股价1.38&lt;5</t>
         </is>
       </c>
     </row>
@@ -4409,17 +4409,17 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>600408</t>
+          <t>600433</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>安泰集团</t>
+          <t>冠豪高新</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.88&lt;5</t>
+          <t>L1-规则3:股价3.53&lt;5</t>
         </is>
       </c>
     </row>
@@ -4429,17 +4429,17 @@
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>600421</t>
+          <t>600436</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>退市华嵘</t>
+          <t>片仔癀</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则4:股价119.56&gt;100</t>
         </is>
       </c>
     </row>
@@ -4449,17 +4449,17 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>600423</t>
+          <t>600439</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>*ST柳化</t>
+          <t>瑞贝卡</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.48&lt;5</t>
+          <t>L1-规则3:股价2.27&lt;5</t>
         </is>
       </c>
     </row>
@@ -4469,17 +4469,17 @@
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>600425</t>
+          <t>600448</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>XD青松建</t>
+          <t>华纺股份</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.54&lt;5</t>
+          <t>L1-规则3:股价2.90&lt;5</t>
         </is>
       </c>
     </row>
@@ -4489,17 +4489,17 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>600429</t>
+          <t>600462</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>三元股份</t>
+          <t>退市九有</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.40&lt;5</t>
+          <t>L1-规则3:股价0.21&lt;5</t>
         </is>
       </c>
     </row>
@@ -4509,17 +4509,17 @@
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>600432</t>
+          <t>600466</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>退市吉恩</t>
+          <t>*ST蓝光</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.38&lt;5</t>
+          <t>L1-规则3:股价0.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>600433</t>
+          <t>600467</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>冠豪高新</t>
+          <t>好当家</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.53&lt;5</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>600436</t>
+          <t>600476</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>片仔癀</t>
+          <t>*ST湘邮</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价119.56&gt;100</t>
+          <t>L1-规则5:ST</t>
         </is>
       </c>
     </row>
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>600439</t>
+          <t>600477</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>瑞贝卡</t>
+          <t>杭萧钢构</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.27&lt;5</t>
+          <t>L1-规则3:股价2.59&lt;5</t>
         </is>
       </c>
     </row>
@@ -4589,17 +4589,17 @@
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>600448</t>
+          <t>600485</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>华纺股份</t>
+          <t>*ST信威</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.90&lt;5</t>
+          <t>L1-规则3:股价1.39&lt;5</t>
         </is>
       </c>
     </row>
@@ -4609,17 +4609,17 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>600462</t>
+          <t>600488</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>退市九有</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.21&lt;5</t>
+          <t>L1-规则3:股价4.76&lt;5</t>
         </is>
       </c>
     </row>
@@ -4629,17 +4629,17 @@
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>600466</t>
+          <t>600491</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>*ST蓝光</t>
+          <t>ST龙元</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.40&lt;5</t>
+          <t>L1-规则3:股价1.31&lt;5</t>
         </is>
       </c>
     </row>
@@ -4649,17 +4649,17 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>600467</t>
+          <t>600495</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>好当家</t>
+          <t>晋西车轴</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则3:股价3.80&lt;5</t>
         </is>
       </c>
     </row>
@@ -4669,17 +4669,17 @@
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>600476</t>
+          <t>600496</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>*ST湘邮</t>
+          <t>精工钢构</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>L1-规则5:ST</t>
+          <t>L1-规则3:股价3.84&lt;5</t>
         </is>
       </c>
     </row>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>600477</t>
+          <t>600497</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>杭萧钢构</t>
+          <t>驰宏锌锗</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.59&lt;5</t>
+          <t>L1-规则11:涨停9.9%</t>
         </is>
       </c>
     </row>
@@ -4709,17 +4709,17 @@
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>600485</t>
+          <t>600500</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>*ST信威</t>
+          <t>中化国际</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.39&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4729,17 +4729,17 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>600502</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>安徽建工</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价4.68&lt;5</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4749,17 @@
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>600488</t>
+          <t>600503</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>华丽家族</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.76&lt;5</t>
+          <t>L1-规则3:股价2.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -4769,17 +4769,17 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>600491</t>
+          <t>600507</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>ST龙元</t>
+          <t>方大特钢</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.31&lt;5</t>
+          <t>L1-规则3:股价4.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -4789,17 +4789,17 @@
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>600495</t>
+          <t>600512</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>晋西车轴</t>
+          <t>腾达建设</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.80&lt;5</t>
+          <t>L1-规则3:股价2.08&lt;5</t>
         </is>
       </c>
     </row>
@@ -4809,17 +4809,17 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>600496</t>
+          <t>600515</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>精工钢构</t>
+          <t>海南机场</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价3.84&lt;5</t>
+          <t>L1-规则3:股价2.98&lt;5</t>
         </is>
       </c>
     </row>
@@ -4829,17 +4829,17 @@
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>600497</t>
+          <t>600517</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>驰宏锌锗</t>
+          <t>国网英大</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停9.9%</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -4849,17 +4849,17 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>600500</t>
+          <t>600518</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>中化国际</t>
+          <t>康美药业</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价1.40&lt;5</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4869,17 @@
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>600502</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>安徽建工</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.68&lt;5</t>
+          <t>L1-规则4:股价1291.91&gt;100</t>
         </is>
       </c>
     </row>
@@ -4889,17 +4889,17 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>600503</t>
+          <t>600525</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>华丽家族</t>
+          <t>ST长园</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.46&lt;5</t>
+          <t>L1-规则3:股价4.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -4909,17 +4909,17 @@
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>600507</t>
+          <t>600526</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>方大特钢</t>
+          <t>菲达环保</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.29&lt;5</t>
+          <t>L1-规则3:股价4.49&lt;5</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>600512</t>
+          <t>600527</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>腾达建设</t>
+          <t>江南高纤</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.08&lt;5</t>
+          <t>L1-规则3:股价2.32&lt;5</t>
         </is>
       </c>
     </row>
@@ -4949,17 +4949,17 @@
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>600515</t>
+          <t>600531</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>海南机场</t>
+          <t>豫光金铅</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.98&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>600517</t>
+          <t>600532</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>国网英大</t>
+          <t>退市未来</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则3:股价0.72&lt;5</t>
         </is>
       </c>
     </row>
@@ -4989,17 +4989,17 @@
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>600518</t>
+          <t>600533</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>康美药业</t>
+          <t>栖霞建设</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.40&lt;5</t>
+          <t>L1-规则3:股价2.19&lt;5</t>
         </is>
       </c>
     </row>
@@ -5009,17 +5009,17 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600536</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中国软件</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价1291.91&gt;100</t>
+          <t>L1-规则22:跌停-10.0%</t>
         </is>
       </c>
     </row>
@@ -5029,17 +5029,17 @@
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>600525</t>
+          <t>600537</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>*ST亿晶</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.99&lt;5</t>
+          <t>L1-规则3:股价2.58&lt;5</t>
         </is>
       </c>
     </row>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>600526</t>
+          <t>600539</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>菲达环保</t>
+          <t>狮头股份</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.49&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5069,17 @@
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>600527</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>江南高纤</t>
+          <t>新赛股份</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.32&lt;5</t>
+          <t>L1-规则3:股价4.46&lt;5</t>
         </is>
       </c>
     </row>
@@ -5089,17 +5089,17 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>600531</t>
+          <t>600543</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>豫光金铅</t>
+          <t>*ST莫高</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价4.22&lt;5</t>
         </is>
       </c>
     </row>
@@ -5109,17 +5109,17 @@
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>600532</t>
+          <t>600555</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>退市未来</t>
+          <t>退市海创</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.72&lt;5</t>
+          <t>L1-规则3:股价0.26&lt;5</t>
         </is>
       </c>
     </row>
@@ -5129,17 +5129,17 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>600533</t>
+          <t>600556</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>栖霞建设</t>
+          <t>天下秀</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.19&lt;5</t>
+          <t>L1-规则3:股价4.89&lt;5</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5149,17 @@
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>600536</t>
+          <t>600563</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>中国软件</t>
+          <t>XD法拉电</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>L1-规则22:跌停-10.0%</t>
+          <t>L1-规则4:股价143.00&gt;100</t>
         </is>
       </c>
     </row>
@@ -5169,17 +5169,17 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>600537</t>
+          <t>600565</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>*ST亿晶</t>
+          <t>ST迪马</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.58&lt;5</t>
+          <t>L1-规则3:股价0.85&lt;5</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5189,17 @@
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>600539</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>狮头股份</t>
+          <t>山鹰国际</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>L1-规则11:涨停10.0%</t>
+          <t>L1-规则3:股价1.44&lt;5</t>
         </is>
       </c>
     </row>
@@ -5209,17 +5209,17 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>600540</t>
+          <t>600568</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>新赛股份</t>
+          <t>ST中珠</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.46&lt;5</t>
+          <t>L1-规则3:股价2.54&lt;5</t>
         </is>
       </c>
     </row>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>600543</t>
+          <t>600569</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>*ST莫高</t>
+          <t>安阳钢铁</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.22&lt;5</t>
+          <t>L1-规则3:股价1.87&lt;5</t>
         </is>
       </c>
     </row>
@@ -5249,17 +5249,17 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>600549</t>
+          <t>600572</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>厦门钨业</t>
+          <t>康恩贝</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>L1-规则13:7日内已推荐</t>
+          <t>L1-规则3:股价4.13&lt;5</t>
         </is>
       </c>
     </row>
@@ -5269,17 +5269,17 @@
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>600555</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>退市海创</t>
+          <t>淮河能源</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.26&lt;5</t>
+          <t>L1-规则3:股价3.99&lt;5</t>
         </is>
       </c>
     </row>
@@ -5289,17 +5289,17 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>600556</t>
+          <t>600576</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>天下秀</t>
+          <t>祥源文旅</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.89&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5309,17 +5309,17 @@
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>600563</t>
+          <t>600581</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>XD法拉电</t>
+          <t>*ST八钢</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>L1-规则4:股价143.00&gt;100</t>
+          <t>L1-规则3:股价2.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5329,17 +5329,17 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>600565</t>
+          <t>600586</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>ST迪马</t>
+          <t>金晶科技</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价0.85&lt;5</t>
+          <t>L1-规则3:股价4.57&lt;5</t>
         </is>
       </c>
     </row>
@@ -5349,17 +5349,17 @@
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>600567</t>
+          <t>600594</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>山鹰国际</t>
+          <t>益佰制药</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.44&lt;5</t>
+          <t>L1-规则3:股价3.29&lt;5</t>
         </is>
       </c>
     </row>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>600568</t>
+          <t>600599</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>ST中珠</t>
+          <t>退市熊猫</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价2.54&lt;5</t>
+          <t>L1-规则3:股价0.41&lt;5</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>600569</t>
+          <t>600601</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>安阳钢铁</t>
+          <t>方正科技</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价1.87&lt;5</t>
+          <t>L1-规则11:涨停10.0%</t>
         </is>
       </c>
     </row>
@@ -5409,17 +5409,17 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>600572</t>
+          <t>600603</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>康恩贝</t>
+          <t>广汇物流</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>L1-规则3:股价4.13&lt;5</t>
+          <t>L1-规则3:股价4.64&lt;5</t>
         </is>
       </c>
     </row>
@@ -5429,215 +5429,15 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>600575</t>
+          <t>600604</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>淮河能源</t>
+          <t>市北高新</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则3:股价3.99&lt;5</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="10" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" s="10" t="inlineStr">
-        <is>
-          <t>600576</t>
-        </is>
-      </c>
-      <c r="C202" s="10" t="inlineStr">
-        <is>
-          <t>祥源文旅</t>
-        </is>
-      </c>
-      <c r="D202" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则11:涨停10.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="10" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" s="10" t="inlineStr">
-        <is>
-          <t>600578</t>
-        </is>
-      </c>
-      <c r="C203" s="10" t="inlineStr">
-        <is>
-          <t>京能电力</t>
-        </is>
-      </c>
-      <c r="D203" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则13:7日内已推荐</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="10" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" s="10" t="inlineStr">
-        <is>
-          <t>600581</t>
-        </is>
-      </c>
-      <c r="C204" s="10" t="inlineStr">
-        <is>
-          <t>*ST八钢</t>
-        </is>
-      </c>
-      <c r="D204" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则3:股价2.57&lt;5</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="10" t="n">
-        <v>204</v>
-      </c>
-      <c r="B205" s="10" t="inlineStr">
-        <is>
-          <t>600586</t>
-        </is>
-      </c>
-      <c r="C205" s="10" t="inlineStr">
-        <is>
-          <t>金晶科技</t>
-        </is>
-      </c>
-      <c r="D205" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则3:股价4.57&lt;5</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="10" t="n">
-        <v>205</v>
-      </c>
-      <c r="B206" s="10" t="inlineStr">
-        <is>
-          <t>600592</t>
-        </is>
-      </c>
-      <c r="C206" s="10" t="inlineStr">
-        <is>
-          <t>龙溪股份</t>
-        </is>
-      </c>
-      <c r="D206" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则13:7日内已推荐</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="10" t="n">
-        <v>206</v>
-      </c>
-      <c r="B207" s="10" t="inlineStr">
-        <is>
-          <t>600594</t>
-        </is>
-      </c>
-      <c r="C207" s="10" t="inlineStr">
-        <is>
-          <t>益佰制药</t>
-        </is>
-      </c>
-      <c r="D207" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则3:股价3.29&lt;5</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="10" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" s="10" t="inlineStr">
-        <is>
-          <t>600599</t>
-        </is>
-      </c>
-      <c r="C208" s="10" t="inlineStr">
-        <is>
-          <t>退市熊猫</t>
-        </is>
-      </c>
-      <c r="D208" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则3:股价0.41&lt;5</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="10" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" s="10" t="inlineStr">
-        <is>
-          <t>600601</t>
-        </is>
-      </c>
-      <c r="C209" s="10" t="inlineStr">
-        <is>
-          <t>方正科技</t>
-        </is>
-      </c>
-      <c r="D209" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则11:涨停10.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="10" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" s="10" t="inlineStr">
-        <is>
-          <t>600603</t>
-        </is>
-      </c>
-      <c r="C210" s="10" t="inlineStr">
-        <is>
-          <t>广汇物流</t>
-        </is>
-      </c>
-      <c r="D210" s="10" t="inlineStr">
-        <is>
-          <t>L1-规则3:股价4.64&lt;5</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" s="10" t="inlineStr">
-        <is>
-          <t>600604</t>
-        </is>
-      </c>
-      <c r="C211" s="10" t="inlineStr">
-        <is>
-          <t>市北高新</t>
-        </is>
-      </c>
-      <c r="D211" s="10" t="inlineStr">
         <is>
           <t>L1-规则3:股价4.22&lt;5</t>
         </is>
@@ -5797,12 +5597,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600438</t>
+          <t>600592</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>通威股份</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5811,7 +5611,7 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>-3.52</v>
+        <v>-5.18</v>
       </c>
       <c r="F2" s="10" t="n"/>
       <c r="G2" s="10" t="n">
@@ -5819,7 +5619,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>跌3.5%(简版)</t>
+          <t>跌5.2%(简版)</t>
         </is>
       </c>
     </row>
@@ -5829,12 +5629,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600520</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>三佳科技</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5843,7 +5643,7 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-6.53</v>
+        <v>-5.27</v>
       </c>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n">
@@ -5851,7 +5651,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>跌6.5%(简版)</t>
+          <t>跌5.3%(简版)</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5661,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600007</t>
+          <t>600234</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>中国国贸</t>
+          <t>科新发展</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5875,7 +5675,7 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-6.92</v>
+        <v>-4.5</v>
       </c>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n">
@@ -5883,7 +5683,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>跌6.9%(简版)</t>
+          <t>跌4.5%(简版)</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5759,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>600438</t>
+          <t>600592</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>通威股份</t>
+          <t>龙溪股份</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -5995,12 +5795,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>600520</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>三佳科技</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -6031,12 +5831,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>600007</t>
+          <t>600234</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>中国国贸</t>
+          <t>科新发展</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -6110,7 +5910,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>600438 通威股份</t>
+          <t>600592 龙溪股份</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -6122,7 +5922,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>600520 三佳科技</t>
+          <t>600487 亨通光电</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -6134,7 +5934,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>600007 中国国贸</t>
+          <t>600234 科新发展</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,27 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF8C00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -43,15 +64,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +79,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,21 +120,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -479,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -594,59 +629,275 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 0 只标的（A:0 B:0 C:0 D:0 E:0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>上海机场</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>600009</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.5%成交额4.8亿</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600009.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>南方航空</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>600029</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.98%成交额10.8亿</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600029.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>600030</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.06%成交额70.3亿</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600030.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 3 只标的（A:60 B:0 C:210 D:0 E:22）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，量&gt;5日均×1.5且&gt;昨日×1.2，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -654,15 +905,20 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A3:R3"/>
     <mergeCell ref="A7:R7"/>
     <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A14:R14"/>
     <mergeCell ref="A9:R9"/>
     <mergeCell ref="A8:R8"/>
     <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A12:R12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -845,59 +845,203 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 3 只标的（A:60 B:0 C:210 D:0 E:22）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>三一重工</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>600031</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.79%成交额21.4亿</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600031.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>中直股份</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>600038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>上海主板</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.7%成交额4.2亿</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600038.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 5 只标的（A:60 B:0 C:210 D:0 E:22）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>策略说明：</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>A 动量延续：涨幅3-7%，量比1.5-3.0，量&gt;5日均×1.5且&gt;昨日×1.2，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
+          <t>A 动量延续：涨幅3-7%，量比1.5-3.0，量&gt;5日均×1.5且&gt;昨日×1.2，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
+          <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -905,19 +1049,21 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A7:R7"/>
+    <mergeCell ref="A16:R16"/>
     <mergeCell ref="A11:R11"/>
     <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A13:R13"/>
     <mergeCell ref="A14:R14"/>
     <mergeCell ref="A9:R9"/>
     <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A6:R6"/>
     <mergeCell ref="A12:R12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +55,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -68,7 +74,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +91,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+        <bgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -137,16 +149,40 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -514,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -650,12 +686,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
@@ -722,12 +758,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
@@ -794,12 +830,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
@@ -866,12 +902,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
@@ -938,12 +974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>上海主板</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -989,59 +1025,2939 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 5 只标的（A:60 B:0 C:210 D:0 E:22）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>同方股份</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>600100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.04%成交额4.6亿</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600100.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>北方稀土</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>600111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.02%成交额75.4亿</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600111.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>浙江东日</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>600113</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.82%成交额2.5亿</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600113.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>兰花科创</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>600123</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.17%成交额2.8亿</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600123.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>国网信通</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>600131</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.38%成交额2.3亿</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600131.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>紫江企业</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>600210</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.77%成交额1.6亿</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600210.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>西藏药业</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>600211</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.63%成交额2.1亿</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600211.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>太龙药业</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>600222</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.81%成交额1.5亿</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600222.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>广汇能源</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>600256</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.27%成交额26.5亿</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600256.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>海正药业</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>600267</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.17%成交额2.1亿</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600267.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>洪都航空</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>600316</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.63%成交额4.2亿</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600316.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>中盐化工</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>600328</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.2%成交额1.7亿</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600328.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>宏达股份</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>600331</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.11%成交额8.4亿</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600331.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>西藏珠峰</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>600338</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.9%成交额21.3亿</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600338.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>中航机载</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>600372</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.82%成交额6.2亿</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600372.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>三友化工</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>600409</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.35%成交额3.1亿</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600409.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>北方导航</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>600435</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.97%成交额4.3亿</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600435.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>宝钛股份</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>600456</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.2%成交额3.9亿</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600456.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>华光环能</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>600475</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.25%成交额2.3亿</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600475.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>科力远</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>600478</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.15%成交额1.9亿</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600478.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>黑牡丹</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>600510</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.09%成交额1.1亿</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600510.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>交大昂立</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>600530</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.55%成交额1.0亿</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600530.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>山东黄金</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>600547</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.12%成交额23.2亿</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600547.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>恒生电子</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>600570</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.28%成交额7.0亿</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600570.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>泰豪科技</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>600590</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>化工</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.06%成交额5.1亿</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600590.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>海立股份</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>600619</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.33%成交额3.9亿</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600619.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>华鑫股份</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>600621</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.5%成交额1.5亿</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600621.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>华谊集团</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>600623</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.46%成交额2.6亿</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600623.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>中船防务</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>600685</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.46%成交额3.6亿</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600685.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>辽宁成大</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>600739</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅4.14%成交额1.9亿</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600739.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦江酒店</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>600754</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.84%成交额2.9亿</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600754.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>安徽合力</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>600761</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.68%成交额2.6亿</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600761.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>通策医疗</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>600763</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>动量延续:涨幅3.07%成交额2.4亿</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600763.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>华建集团</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>600629</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>回调企稳:涨幅0.06%成交额3.3亿</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600629.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>中交设计</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>600720</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>回调企稳:涨幅0.36%成交额1.2亿</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="R41" s="9" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600720.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>华新建材</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>600801</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>事件驱动:涨幅1.39%成交额2.6亿</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O42" s="10" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="P42" s="10" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="Q42" s="10" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600801.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>新奥股份</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>600803</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I43" s="10" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>事件驱动:涨幅0.55%成交额2.2亿</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N43" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O43" s="10" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="P43" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Q43" s="10" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600803.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>神马股份</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>600810</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>事件驱动:涨幅2.4%成交额2.3亿</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O44" s="10" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="P44" s="10" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Q44" s="10" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600810.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>杭州解百</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>600814</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="I45" s="10" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>事件驱动(小盘):涨幅2.22%</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O45" s="10" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="P45" s="10" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600814.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>隧道股份</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>600820</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>事件驱动:涨幅2.61%成交额1.2亿</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O46" s="10" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="P46" s="10" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q46" s="10" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600820.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 45 只标的（A:38 B:0 C:5 D:0 E:2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，量&gt;5日均×1.5且&gt;昨日×1.2，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认，股价≥MA60 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -1049,14 +3965,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A10:R10"/>
-    <mergeCell ref="A13:R13"/>
-    <mergeCell ref="A14:R14"/>
-    <mergeCell ref="A9:R9"/>
-    <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="A48:R48"/>
+    <mergeCell ref="A53:R53"/>
+    <mergeCell ref="A54:R54"/>
+    <mergeCell ref="A49:R49"/>
+    <mergeCell ref="A52:R52"/>
+    <mergeCell ref="A51:R51"/>
+    <mergeCell ref="A56:R56"/>
+    <mergeCell ref="A50:R50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
@@ -1064,6 +3980,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,31 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BF8F00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -43,15 +68,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +83,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,21 +124,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -479,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -594,57 +636,273 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 0 只标的（A:0 B:0 C:0 D:0 E:0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>中远海能</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>600026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>涨幅适中+1</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>中直股份</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>600038</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>涨幅适中+1</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600038.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>五矿发展</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>600058</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>涨幅适中+1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600058.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 3 只标的（A:3 B:0 C:0 D:0 E:0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -652,15 +910,20 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A3:R3"/>
     <mergeCell ref="A7:R7"/>
     <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A14:R14"/>
     <mergeCell ref="A9:R9"/>
     <mergeCell ref="A8:R8"/>
     <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A12:R12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -72,7 +78,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +95,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -124,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,16 +162,46 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -521,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -647,12 +695,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>中远海能</t>
+          <t>紫江企业</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600026</t>
+          <t>600210</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -666,19 +714,19 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>5.11</v>
+        <v>3.77</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16.93</v>
+        <v>6.39</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5.71</v>
+        <v>3.77</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -694,17 +742,17 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>16.8</v>
+        <v>6.34</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>18.38</v>
+        <v>6.93</v>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600026.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600210.html</t>
         </is>
       </c>
     </row>
@@ -719,12 +767,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>中直股份</t>
+          <t>太龙药业</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600038</t>
+          <t>600222</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -738,19 +786,19 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4.7</v>
+        <v>3.81</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>27.36</v>
+        <v>7.68</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>28.53</v>
+        <v>7.9</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.73</v>
+        <v>4.2</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -766,143 +814,359 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>28.53</v>
+        <v>7.9</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>27.39</v>
+        <v>7.58</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>29.96</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600038.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600222.html</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>五矿发展</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>600058</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>白云机场</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>600004</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J4" s="2" t="n">
+      <c r="G4" s="9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>涨幅适中+1</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>https://quote.eastmoney.com/concept/sh600058.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 3 只标的（A:3 B:0 C:0 D:0 E:0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="K4" s="7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>策略E匹配</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600004.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>中国医药</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>600056</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>策略E匹配</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="R5" s="11" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600056.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>浦发银行</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>600000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>策略D匹配</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="P6" s="12" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="Q6" s="12" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600000.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>上港集团</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>600018</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>策略D匹配</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="P7" s="12" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Q7" s="12" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600018.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 6 只标的（A:2 B:0 C:0 D:2 E:2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -910,19 +1174,22 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A7:R7"/>
+    <mergeCell ref="A15:R15"/>
     <mergeCell ref="A11:R11"/>
     <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A13:R13"/>
     <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A17:R17"/>
     <mergeCell ref="A9:R9"/>
-    <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A6:R6"/>
     <mergeCell ref="A12:R12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -47,7 +47,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00BF8F00"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
@@ -58,8 +59,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00BF8F00"/>
       <sz val="10"/>
     </font>
     <font>
@@ -695,12 +695,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>紫江企业</t>
+          <t>石大胜华</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>600210</t>
+          <t>603026</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -714,45 +714,45 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.77</v>
+        <v>5.46</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6.39</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6.6</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3.77</v>
+        <v>7.52</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>涨幅适中+1</t>
+          <t>涨幅适中+2; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>6.6</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>6.34</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>6.93</v>
+        <v>90.67</v>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600210.html</t>
+          <t>https://quote.eastmoney.com/concept/sh603026.html</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>太龙药业</t>
+          <t>应流股份</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>600222</t>
+          <t>603308</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -786,45 +786,45 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>3.81</v>
+        <v>4.81</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.68</v>
+        <v>59.47</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7.9</v>
+        <v>60.15</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.2</v>
+        <v>7.93</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>涨幅适中+1</t>
+          <t>涨幅适中+2; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>7.9</v>
+        <v>60.15</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>7.58</v>
+        <v>57.74</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>63.16</v>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600222.html</t>
+          <t>https://quote.eastmoney.com/concept/sh603308.html</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>白云机场</t>
+          <t>交通银行</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>600004</t>
+          <t>601328</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -858,45 +858,45 @@
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>8.119999999999999</v>
+        <v>6.93</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>8.26</v>
+        <v>7.14</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>3.24</v>
+        <v>3.87</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>策略E匹配</t>
+          <t>温和突破+1; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="O4" s="7" t="n">
-        <v>8.26</v>
+        <v>7.14</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>7.85</v>
+        <v>6.78</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>8.67</v>
+        <v>7.5</v>
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600004.html</t>
+          <t>https://quote.eastmoney.com/concept/sh601328.html</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>中国医药</t>
+          <t>盛和资源</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>600056</t>
+          <t>600392</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -930,45 +930,45 @@
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>8.91</v>
+        <v>25.45</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>9.15</v>
+        <v>25.8</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>2.8</v>
+        <v>6.25</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>策略E匹配</t>
+          <t>温和突破+1; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
         </is>
       </c>
       <c r="M5" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="O5" s="7" t="n">
-        <v>9.15</v>
+        <v>25.8</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>8.69</v>
+        <v>24.51</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>9.609999999999999</v>
+        <v>27.09</v>
       </c>
       <c r="R5" s="11" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600056.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600392.html</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>浦发银行</t>
+          <t>中国银行</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>601988</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1002,45 +1002,45 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>9.5</v>
+        <v>6.14</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>9.67</v>
+        <v>6.29</v>
       </c>
       <c r="J6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>策略D匹配</t>
+          <t>温和涨幅+1; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
         </is>
       </c>
       <c r="M6" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N6" s="15" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="O6" s="12" t="n">
-        <v>9.67</v>
+        <v>6.29</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>9.19</v>
+        <v>5.98</v>
       </c>
       <c r="Q6" s="12" t="n">
-        <v>10.06</v>
+        <v>6.54</v>
       </c>
       <c r="R6" s="16" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600000.html</t>
+          <t>https://quote.eastmoney.com/concept/sh601988.html</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>上港集团</t>
+          <t>中国船舶</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>600018</t>
+          <t>600150</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -1074,45 +1074,45 @@
         </is>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>4.98</v>
+        <v>34.7</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>5.04</v>
+        <v>34.89</v>
       </c>
       <c r="J7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>2.21</v>
+        <v>3.02</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>策略D匹配</t>
+          <t>温和涨幅+1; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
         </is>
       </c>
       <c r="M7" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N7" s="15" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="O7" s="12" t="n">
-        <v>5.04</v>
+        <v>34.89</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>4.79</v>
+        <v>33.15</v>
       </c>
       <c r="Q7" s="12" t="n">
-        <v>5.24</v>
+        <v>36.29</v>
       </c>
       <c r="R7" s="16" t="inlineStr">
         <is>
-          <t>https://quote.eastmoney.com/concept/sh600018.html</t>
+          <t>https://quote.eastmoney.com/concept/sh600150.html</t>
         </is>
       </c>
     </row>

--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,37 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BF8F00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -43,15 +74,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +89,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,21 +142,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -479,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -594,57 +684,489 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>📊 共筛选出 0 只标的（A:0 B:0 C:0 D:0 E:0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>中国铝业</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>601600</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>涨幅适中+2; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh601600.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>中国人寿</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>601628</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>涨幅适中+2; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh601628.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>国联民生</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>601456</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>温和涨幅+1; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh601456.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>600418</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>温和涨幅+1; 活跃度高+1; 振幅适中+1; 收盘强势+1</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="R5" s="11" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh600418.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>601318</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>活跃度高+1; 振幅适中+1; 收盘强势+1</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="P6" s="12" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="Q6" s="12" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh601318.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>中国中免</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>601888</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>活跃度高+1; 振幅适中+1; 收盘强势+1</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="P7" s="12" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="Q7" s="12" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <t>https://quote.eastmoney.com/concept/sh601888.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>📊 共筛选出 6 只标的（A:2 B:0 C:0 D:2 E:2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>策略说明：</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>A 动量延续：涨幅3-7%，量比1.5-3.0，MA5&gt;MA10&gt;MA20 — 仓位强35-40%/震荡12-17%/弱关闭</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>B 超跌反弹：连跌≥3日，量&lt;5日均×0.6，RSI(14)&lt;35，KDJ(K&lt;20且J拐头)，站上MA5+放量确认 — 仓位强10-12%/震荡12-15%/弱12-15%</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>C 事件驱动：重大合同/预增&gt;50%/部委级政策，事件时效5级衰减 — 仓位强10-12%/震荡10-12%/弱5-8%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>D 资金埋伏：北向3日连续净买+主力流入&gt;3000万+涨幅&lt;2% — 仓位强5-8%/震荡5-8%/弱3-5%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>E 回调企稳突破：20日内创新高+回调MA20±3%+连3日缩量+站回MA5放量 — 仓位强10-12%/震荡12-15%/弱8-12%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>⚠️ 仅供参考，不构成投资建议</t>
         </is>
@@ -652,15 +1174,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A7:R7"/>
+    <mergeCell ref="A15:R15"/>
     <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A13:R13"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A17:R17"/>
     <mergeCell ref="A9:R9"/>
-    <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A12:R12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/短线标的_2026-06-15.xlsx
+++ b/短线标的_2026-06-15.xlsx
@@ -705,12 +705,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>铝</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
@@ -777,12 +777,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>非银金融</t>
         </is>
       </c>
       <c r="G3" s="4" t="n">
@@ -849,12 +849,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>非银金融</t>
         </is>
       </c>
       <c r="G4" s="9" t="n">
@@ -921,12 +921,12 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>商用车</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>汽车</t>
         </is>
       </c>
       <c r="G5" s="9" t="n">
@@ -993,12 +993,12 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>非银金融</t>
         </is>
       </c>
       <c r="G6" s="14" t="n">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>旅游零售</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>商贸零售</t>
         </is>
       </c>
       <c r="G7" s="14" t="n">
@@ -1116,6 +1116,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
@@ -1165,6 +1166,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="20" t="inlineStr">
         <is>
